--- a/수도명가 보급형 황동수전 판매단가.xlsx
+++ b/수도명가 보급형 황동수전 판매단가.xlsx
@@ -8,16 +8,17 @@
   <sheets>
     <sheet name="자재판매가산출" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="상품판매가산출" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="유통가 보고" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="사용안내" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="설정" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="월평균환율" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="태성재판매가산출" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="유통가 보고" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="사용안내" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="설정" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="월평균환율" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'유통가 보고'!$B$6:$K$26</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'유통가 보고'!$6:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'유통가 보고'!$B$2:$K$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'유통가 보고'!$B$6:$K$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'유통가 보고'!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'유통가 보고'!$B$2:$K$27</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -32,7 +33,7 @@
     <numFmt numFmtId="167" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="168" formatCode="#,##0;(#,##0);-"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -271,6 +272,11 @@
       <color rgb="0014606B"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -804,7 +810,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1073,13 +1079,28 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="33" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="28" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="28" fillId="8" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="31" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="30" fillId="10" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="30" fillId="10" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="30" fillId="10" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1"/>
     <cellStyle name="메모 2" xfId="2"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <font>
         <name val="맑은 고딕"/>
@@ -1125,6 +1146,13 @@
           <fgColor rgb="00FFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="맑은 고딕"/>
+        <color rgb="00C55A11"/>
+        <sz val="10"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1651,6 +1679,15 @@
 얹을 것이 없으므로 0%가 맞습니다.</t>
       </text>
     </comment>
+    <comment ref="C32" authorId="0" shapeId="0">
+      <text>
+        <t>태성 재판매가산출 시트에만 쓰입니다.
+태성 입고가(= 플로우텍 판매단가)가 곧 원가이므로
+추가 비용이 없으면 0%로 두세요.
+계산 방식(C26) · 절상 단위(C27) · 소비자 마진율(C28)은
+상품 판매가와 같은 값을 씁니다.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -4591,6 +4628,1595 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:W34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="170" t="inlineStr">
+        <is>
+          <t>태성 재판매가 산출 — 플로우텍 공급가를 원가로</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="162">
+        <f>"태성 입고가(= 플로우텍 판매단가) → 추가비용 "&amp;TEXT(설정!$C$32,"0.0%")&amp;" → 판관비 "&amp;TEXT(설정!$C$33,"0.0%")&amp;" → BEP 가격 → 영업이익 "&amp;TEXT(설정!$C$34,"0.0%")&amp;" → 기준 판매가 → (영업) 최종 판매가   ·   "&amp;설정!$C$26&amp;" 방식"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="B5" s="128" t="inlineStr">
+        <is>
+          <t>품목</t>
+        </is>
+      </c>
+      <c r="C5" s="128" t="inlineStr">
+        <is>
+          <t>품목코드</t>
+        </is>
+      </c>
+      <c r="D5" s="128" t="inlineStr">
+        <is>
+          <t>조회 입고가</t>
+        </is>
+      </c>
+      <c r="E5" s="128" t="inlineStr">
+        <is>
+          <t>입고가
+직접 입력</t>
+        </is>
+      </c>
+      <c r="F5" s="128" t="inlineStr">
+        <is>
+          <t>적용 입고가</t>
+        </is>
+      </c>
+      <c r="G5" s="128" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="H5" s="128" t="inlineStr">
+        <is>
+          <t>매입원가
+/개</t>
+        </is>
+      </c>
+      <c r="I5" s="128" t="inlineStr">
+        <is>
+          <t>판관비율</t>
+        </is>
+      </c>
+      <c r="J5" s="128" t="inlineStr">
+        <is>
+          <t>영업이익률</t>
+        </is>
+      </c>
+      <c r="K5" s="128" t="inlineStr">
+        <is>
+          <t>BEP 가격</t>
+        </is>
+      </c>
+      <c r="L5" s="128" t="inlineStr">
+        <is>
+          <t>기준 판매가</t>
+        </is>
+      </c>
+      <c r="M5" s="128" t="inlineStr">
+        <is>
+          <t>최종 판매가
+(영업 입력)</t>
+        </is>
+      </c>
+      <c r="N5" s="128" t="inlineStr">
+        <is>
+          <t>적용가</t>
+        </is>
+      </c>
+      <c r="O5" s="128" t="inlineStr">
+        <is>
+          <t>판관비
+/개</t>
+        </is>
+      </c>
+      <c r="P5" s="128" t="inlineStr">
+        <is>
+          <t>영업이익
+/개</t>
+        </is>
+      </c>
+      <c r="Q5" s="128" t="inlineStr">
+        <is>
+          <t>영업이익률
+(실제)</t>
+        </is>
+      </c>
+      <c r="R5" s="128" t="inlineStr">
+        <is>
+          <t>기준가 대비</t>
+        </is>
+      </c>
+      <c r="S5" s="128" t="inlineStr">
+        <is>
+          <t>BEP 대비</t>
+        </is>
+      </c>
+      <c r="T5" s="128" t="inlineStr">
+        <is>
+          <t>소비자
+마진율</t>
+        </is>
+      </c>
+      <c r="U5" s="128" t="inlineStr">
+        <is>
+          <t>소비자 판매가</t>
+        </is>
+      </c>
+      <c r="V5" s="128" t="inlineStr">
+        <is>
+          <t>매출 합계</t>
+        </is>
+      </c>
+      <c r="W5" s="128" t="inlineStr">
+        <is>
+          <t>영업이익 합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="171" t="n"/>
+      <c r="C6" s="171" t="n"/>
+      <c r="D6" s="172">
+        <f>IF($C6="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C6,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E6" s="173" t="n"/>
+      <c r="F6" s="133">
+        <f>IF($E6&lt;&gt;"",$E6,IF(N($D6)=0,"",$D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="174" t="n"/>
+      <c r="H6" s="133">
+        <f>IF($F6="","",$F6*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I6" s="132" t="n"/>
+      <c r="J6" s="132" t="n"/>
+      <c r="K6" s="133">
+        <f>IF($H6="","",IFERROR(IF(설정!$C$26="원가 가산",$H6*(1+IF($I6="",설정!$C$33,$I6)),$H6/(1-IF($I6="",설정!$C$33,$I6))),0))</f>
+        <v/>
+      </c>
+      <c r="L6" s="133">
+        <f>IF($H6="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K6*(1+IF($J6="",설정!$C$34,$J6)),$H6/(1-IF($I6="",설정!$C$33,$I6)-IF($J6="",설정!$C$34,$J6))),0),CEILING(IF(설정!$C$26="원가 가산",$K6*(1+IF($J6="",설정!$C$34,$J6)),$H6/(1-IF($I6="",설정!$C$33,$I6)-IF($J6="",설정!$C$34,$J6))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M6" s="175" t="n"/>
+      <c r="N6" s="133">
+        <f>IF($L6="","",IF($M6="",$L6,$M6))</f>
+        <v/>
+      </c>
+      <c r="O6" s="133">
+        <f>IF($N6="","",IF(설정!$C$26="원가 가산",$H6*IF($I6="",설정!$C$33,$I6),$N6*IF($I6="",설정!$C$33,$I6)))</f>
+        <v/>
+      </c>
+      <c r="P6" s="133">
+        <f>IF($N6="","",$N6-$H6-$O6)</f>
+        <v/>
+      </c>
+      <c r="Q6" s="176">
+        <f>IF(N($N6)=0,"",$P6/$N6)</f>
+        <v/>
+      </c>
+      <c r="R6" s="176">
+        <f>IF(N($L6)=0,"",$N6/$L6-1)</f>
+        <v/>
+      </c>
+      <c r="S6" s="176">
+        <f>IF(N($K6)=0,"",$N6/$K6-1)</f>
+        <v/>
+      </c>
+      <c r="T6" s="132" t="n"/>
+      <c r="U6" s="133">
+        <f>IF($N6="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N6*(1+IF($T6="",설정!$C$28,$T6)),$N6/(1-IF($T6="",설정!$C$28,$T6))),0),CEILING(IF(설정!$C$26="원가 가산",$N6*(1+IF($T6="",설정!$C$28,$T6)),$N6/(1-IF($T6="",설정!$C$28,$T6))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V6" s="133">
+        <f>IF($N6="","",$N6*$G6)</f>
+        <v/>
+      </c>
+      <c r="W6" s="133">
+        <f>IF($P6="","",$P6*$G6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="171" t="n"/>
+      <c r="C7" s="171" t="n"/>
+      <c r="D7" s="172">
+        <f>IF($C7="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C7,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E7" s="173" t="n"/>
+      <c r="F7" s="133">
+        <f>IF($E7&lt;&gt;"",$E7,IF(N($D7)=0,"",$D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="174" t="n"/>
+      <c r="H7" s="133">
+        <f>IF($F7="","",$F7*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I7" s="132" t="n"/>
+      <c r="J7" s="132" t="n"/>
+      <c r="K7" s="133">
+        <f>IF($H7="","",IFERROR(IF(설정!$C$26="원가 가산",$H7*(1+IF($I7="",설정!$C$33,$I7)),$H7/(1-IF($I7="",설정!$C$33,$I7))),0))</f>
+        <v/>
+      </c>
+      <c r="L7" s="133">
+        <f>IF($H7="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K7*(1+IF($J7="",설정!$C$34,$J7)),$H7/(1-IF($I7="",설정!$C$33,$I7)-IF($J7="",설정!$C$34,$J7))),0),CEILING(IF(설정!$C$26="원가 가산",$K7*(1+IF($J7="",설정!$C$34,$J7)),$H7/(1-IF($I7="",설정!$C$33,$I7)-IF($J7="",설정!$C$34,$J7))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M7" s="175" t="n"/>
+      <c r="N7" s="133">
+        <f>IF($L7="","",IF($M7="",$L7,$M7))</f>
+        <v/>
+      </c>
+      <c r="O7" s="133">
+        <f>IF($N7="","",IF(설정!$C$26="원가 가산",$H7*IF($I7="",설정!$C$33,$I7),$N7*IF($I7="",설정!$C$33,$I7)))</f>
+        <v/>
+      </c>
+      <c r="P7" s="133">
+        <f>IF($N7="","",$N7-$H7-$O7)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="176">
+        <f>IF(N($N7)=0,"",$P7/$N7)</f>
+        <v/>
+      </c>
+      <c r="R7" s="176">
+        <f>IF(N($L7)=0,"",$N7/$L7-1)</f>
+        <v/>
+      </c>
+      <c r="S7" s="176">
+        <f>IF(N($K7)=0,"",$N7/$K7-1)</f>
+        <v/>
+      </c>
+      <c r="T7" s="132" t="n"/>
+      <c r="U7" s="133">
+        <f>IF($N7="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N7*(1+IF($T7="",설정!$C$28,$T7)),$N7/(1-IF($T7="",설정!$C$28,$T7))),0),CEILING(IF(설정!$C$26="원가 가산",$N7*(1+IF($T7="",설정!$C$28,$T7)),$N7/(1-IF($T7="",설정!$C$28,$T7))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V7" s="133">
+        <f>IF($N7="","",$N7*$G7)</f>
+        <v/>
+      </c>
+      <c r="W7" s="133">
+        <f>IF($P7="","",$P7*$G7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="171" t="n"/>
+      <c r="C8" s="171" t="n"/>
+      <c r="D8" s="172">
+        <f>IF($C8="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C8,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E8" s="173" t="n"/>
+      <c r="F8" s="133">
+        <f>IF($E8&lt;&gt;"",$E8,IF(N($D8)=0,"",$D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="174" t="n"/>
+      <c r="H8" s="133">
+        <f>IF($F8="","",$F8*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I8" s="132" t="n"/>
+      <c r="J8" s="132" t="n"/>
+      <c r="K8" s="133">
+        <f>IF($H8="","",IFERROR(IF(설정!$C$26="원가 가산",$H8*(1+IF($I8="",설정!$C$33,$I8)),$H8/(1-IF($I8="",설정!$C$33,$I8))),0))</f>
+        <v/>
+      </c>
+      <c r="L8" s="133">
+        <f>IF($H8="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K8*(1+IF($J8="",설정!$C$34,$J8)),$H8/(1-IF($I8="",설정!$C$33,$I8)-IF($J8="",설정!$C$34,$J8))),0),CEILING(IF(설정!$C$26="원가 가산",$K8*(1+IF($J8="",설정!$C$34,$J8)),$H8/(1-IF($I8="",설정!$C$33,$I8)-IF($J8="",설정!$C$34,$J8))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M8" s="175" t="n"/>
+      <c r="N8" s="133">
+        <f>IF($L8="","",IF($M8="",$L8,$M8))</f>
+        <v/>
+      </c>
+      <c r="O8" s="133">
+        <f>IF($N8="","",IF(설정!$C$26="원가 가산",$H8*IF($I8="",설정!$C$33,$I8),$N8*IF($I8="",설정!$C$33,$I8)))</f>
+        <v/>
+      </c>
+      <c r="P8" s="133">
+        <f>IF($N8="","",$N8-$H8-$O8)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="176">
+        <f>IF(N($N8)=0,"",$P8/$N8)</f>
+        <v/>
+      </c>
+      <c r="R8" s="176">
+        <f>IF(N($L8)=0,"",$N8/$L8-1)</f>
+        <v/>
+      </c>
+      <c r="S8" s="176">
+        <f>IF(N($K8)=0,"",$N8/$K8-1)</f>
+        <v/>
+      </c>
+      <c r="T8" s="132" t="n"/>
+      <c r="U8" s="133">
+        <f>IF($N8="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N8*(1+IF($T8="",설정!$C$28,$T8)),$N8/(1-IF($T8="",설정!$C$28,$T8))),0),CEILING(IF(설정!$C$26="원가 가산",$N8*(1+IF($T8="",설정!$C$28,$T8)),$N8/(1-IF($T8="",설정!$C$28,$T8))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V8" s="133">
+        <f>IF($N8="","",$N8*$G8)</f>
+        <v/>
+      </c>
+      <c r="W8" s="133">
+        <f>IF($P8="","",$P8*$G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="171" t="n"/>
+      <c r="C9" s="171" t="n"/>
+      <c r="D9" s="172">
+        <f>IF($C9="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C9,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E9" s="173" t="n"/>
+      <c r="F9" s="133">
+        <f>IF($E9&lt;&gt;"",$E9,IF(N($D9)=0,"",$D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="174" t="n"/>
+      <c r="H9" s="133">
+        <f>IF($F9="","",$F9*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I9" s="132" t="n"/>
+      <c r="J9" s="132" t="n"/>
+      <c r="K9" s="133">
+        <f>IF($H9="","",IFERROR(IF(설정!$C$26="원가 가산",$H9*(1+IF($I9="",설정!$C$33,$I9)),$H9/(1-IF($I9="",설정!$C$33,$I9))),0))</f>
+        <v/>
+      </c>
+      <c r="L9" s="133">
+        <f>IF($H9="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K9*(1+IF($J9="",설정!$C$34,$J9)),$H9/(1-IF($I9="",설정!$C$33,$I9)-IF($J9="",설정!$C$34,$J9))),0),CEILING(IF(설정!$C$26="원가 가산",$K9*(1+IF($J9="",설정!$C$34,$J9)),$H9/(1-IF($I9="",설정!$C$33,$I9)-IF($J9="",설정!$C$34,$J9))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M9" s="175" t="n"/>
+      <c r="N9" s="133">
+        <f>IF($L9="","",IF($M9="",$L9,$M9))</f>
+        <v/>
+      </c>
+      <c r="O9" s="133">
+        <f>IF($N9="","",IF(설정!$C$26="원가 가산",$H9*IF($I9="",설정!$C$33,$I9),$N9*IF($I9="",설정!$C$33,$I9)))</f>
+        <v/>
+      </c>
+      <c r="P9" s="133">
+        <f>IF($N9="","",$N9-$H9-$O9)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="176">
+        <f>IF(N($N9)=0,"",$P9/$N9)</f>
+        <v/>
+      </c>
+      <c r="R9" s="176">
+        <f>IF(N($L9)=0,"",$N9/$L9-1)</f>
+        <v/>
+      </c>
+      <c r="S9" s="176">
+        <f>IF(N($K9)=0,"",$N9/$K9-1)</f>
+        <v/>
+      </c>
+      <c r="T9" s="132" t="n"/>
+      <c r="U9" s="133">
+        <f>IF($N9="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N9*(1+IF($T9="",설정!$C$28,$T9)),$N9/(1-IF($T9="",설정!$C$28,$T9))),0),CEILING(IF(설정!$C$26="원가 가산",$N9*(1+IF($T9="",설정!$C$28,$T9)),$N9/(1-IF($T9="",설정!$C$28,$T9))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V9" s="133">
+        <f>IF($N9="","",$N9*$G9)</f>
+        <v/>
+      </c>
+      <c r="W9" s="133">
+        <f>IF($P9="","",$P9*$G9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="171" t="n"/>
+      <c r="C10" s="171" t="n"/>
+      <c r="D10" s="172">
+        <f>IF($C10="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C10,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E10" s="173" t="n"/>
+      <c r="F10" s="133">
+        <f>IF($E10&lt;&gt;"",$E10,IF(N($D10)=0,"",$D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="174" t="n"/>
+      <c r="H10" s="133">
+        <f>IF($F10="","",$F10*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I10" s="132" t="n"/>
+      <c r="J10" s="132" t="n"/>
+      <c r="K10" s="133">
+        <f>IF($H10="","",IFERROR(IF(설정!$C$26="원가 가산",$H10*(1+IF($I10="",설정!$C$33,$I10)),$H10/(1-IF($I10="",설정!$C$33,$I10))),0))</f>
+        <v/>
+      </c>
+      <c r="L10" s="133">
+        <f>IF($H10="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K10*(1+IF($J10="",설정!$C$34,$J10)),$H10/(1-IF($I10="",설정!$C$33,$I10)-IF($J10="",설정!$C$34,$J10))),0),CEILING(IF(설정!$C$26="원가 가산",$K10*(1+IF($J10="",설정!$C$34,$J10)),$H10/(1-IF($I10="",설정!$C$33,$I10)-IF($J10="",설정!$C$34,$J10))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M10" s="175" t="n"/>
+      <c r="N10" s="133">
+        <f>IF($L10="","",IF($M10="",$L10,$M10))</f>
+        <v/>
+      </c>
+      <c r="O10" s="133">
+        <f>IF($N10="","",IF(설정!$C$26="원가 가산",$H10*IF($I10="",설정!$C$33,$I10),$N10*IF($I10="",설정!$C$33,$I10)))</f>
+        <v/>
+      </c>
+      <c r="P10" s="133">
+        <f>IF($N10="","",$N10-$H10-$O10)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="176">
+        <f>IF(N($N10)=0,"",$P10/$N10)</f>
+        <v/>
+      </c>
+      <c r="R10" s="176">
+        <f>IF(N($L10)=0,"",$N10/$L10-1)</f>
+        <v/>
+      </c>
+      <c r="S10" s="176">
+        <f>IF(N($K10)=0,"",$N10/$K10-1)</f>
+        <v/>
+      </c>
+      <c r="T10" s="132" t="n"/>
+      <c r="U10" s="133">
+        <f>IF($N10="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N10*(1+IF($T10="",설정!$C$28,$T10)),$N10/(1-IF($T10="",설정!$C$28,$T10))),0),CEILING(IF(설정!$C$26="원가 가산",$N10*(1+IF($T10="",설정!$C$28,$T10)),$N10/(1-IF($T10="",설정!$C$28,$T10))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V10" s="133">
+        <f>IF($N10="","",$N10*$G10)</f>
+        <v/>
+      </c>
+      <c r="W10" s="133">
+        <f>IF($P10="","",$P10*$G10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="171" t="n"/>
+      <c r="C11" s="171" t="n"/>
+      <c r="D11" s="172">
+        <f>IF($C11="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C11,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E11" s="173" t="n"/>
+      <c r="F11" s="133">
+        <f>IF($E11&lt;&gt;"",$E11,IF(N($D11)=0,"",$D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="174" t="n"/>
+      <c r="H11" s="133">
+        <f>IF($F11="","",$F11*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I11" s="132" t="n"/>
+      <c r="J11" s="132" t="n"/>
+      <c r="K11" s="133">
+        <f>IF($H11="","",IFERROR(IF(설정!$C$26="원가 가산",$H11*(1+IF($I11="",설정!$C$33,$I11)),$H11/(1-IF($I11="",설정!$C$33,$I11))),0))</f>
+        <v/>
+      </c>
+      <c r="L11" s="133">
+        <f>IF($H11="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K11*(1+IF($J11="",설정!$C$34,$J11)),$H11/(1-IF($I11="",설정!$C$33,$I11)-IF($J11="",설정!$C$34,$J11))),0),CEILING(IF(설정!$C$26="원가 가산",$K11*(1+IF($J11="",설정!$C$34,$J11)),$H11/(1-IF($I11="",설정!$C$33,$I11)-IF($J11="",설정!$C$34,$J11))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M11" s="175" t="n"/>
+      <c r="N11" s="133">
+        <f>IF($L11="","",IF($M11="",$L11,$M11))</f>
+        <v/>
+      </c>
+      <c r="O11" s="133">
+        <f>IF($N11="","",IF(설정!$C$26="원가 가산",$H11*IF($I11="",설정!$C$33,$I11),$N11*IF($I11="",설정!$C$33,$I11)))</f>
+        <v/>
+      </c>
+      <c r="P11" s="133">
+        <f>IF($N11="","",$N11-$H11-$O11)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="176">
+        <f>IF(N($N11)=0,"",$P11/$N11)</f>
+        <v/>
+      </c>
+      <c r="R11" s="176">
+        <f>IF(N($L11)=0,"",$N11/$L11-1)</f>
+        <v/>
+      </c>
+      <c r="S11" s="176">
+        <f>IF(N($K11)=0,"",$N11/$K11-1)</f>
+        <v/>
+      </c>
+      <c r="T11" s="132" t="n"/>
+      <c r="U11" s="133">
+        <f>IF($N11="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N11*(1+IF($T11="",설정!$C$28,$T11)),$N11/(1-IF($T11="",설정!$C$28,$T11))),0),CEILING(IF(설정!$C$26="원가 가산",$N11*(1+IF($T11="",설정!$C$28,$T11)),$N11/(1-IF($T11="",설정!$C$28,$T11))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V11" s="133">
+        <f>IF($N11="","",$N11*$G11)</f>
+        <v/>
+      </c>
+      <c r="W11" s="133">
+        <f>IF($P11="","",$P11*$G11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="171" t="n"/>
+      <c r="C12" s="171" t="n"/>
+      <c r="D12" s="172">
+        <f>IF($C12="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C12,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E12" s="173" t="n"/>
+      <c r="F12" s="133">
+        <f>IF($E12&lt;&gt;"",$E12,IF(N($D12)=0,"",$D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="174" t="n"/>
+      <c r="H12" s="133">
+        <f>IF($F12="","",$F12*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I12" s="132" t="n"/>
+      <c r="J12" s="132" t="n"/>
+      <c r="K12" s="133">
+        <f>IF($H12="","",IFERROR(IF(설정!$C$26="원가 가산",$H12*(1+IF($I12="",설정!$C$33,$I12)),$H12/(1-IF($I12="",설정!$C$33,$I12))),0))</f>
+        <v/>
+      </c>
+      <c r="L12" s="133">
+        <f>IF($H12="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K12*(1+IF($J12="",설정!$C$34,$J12)),$H12/(1-IF($I12="",설정!$C$33,$I12)-IF($J12="",설정!$C$34,$J12))),0),CEILING(IF(설정!$C$26="원가 가산",$K12*(1+IF($J12="",설정!$C$34,$J12)),$H12/(1-IF($I12="",설정!$C$33,$I12)-IF($J12="",설정!$C$34,$J12))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M12" s="175" t="n"/>
+      <c r="N12" s="133">
+        <f>IF($L12="","",IF($M12="",$L12,$M12))</f>
+        <v/>
+      </c>
+      <c r="O12" s="133">
+        <f>IF($N12="","",IF(설정!$C$26="원가 가산",$H12*IF($I12="",설정!$C$33,$I12),$N12*IF($I12="",설정!$C$33,$I12)))</f>
+        <v/>
+      </c>
+      <c r="P12" s="133">
+        <f>IF($N12="","",$N12-$H12-$O12)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="176">
+        <f>IF(N($N12)=0,"",$P12/$N12)</f>
+        <v/>
+      </c>
+      <c r="R12" s="176">
+        <f>IF(N($L12)=0,"",$N12/$L12-1)</f>
+        <v/>
+      </c>
+      <c r="S12" s="176">
+        <f>IF(N($K12)=0,"",$N12/$K12-1)</f>
+        <v/>
+      </c>
+      <c r="T12" s="132" t="n"/>
+      <c r="U12" s="133">
+        <f>IF($N12="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N12*(1+IF($T12="",설정!$C$28,$T12)),$N12/(1-IF($T12="",설정!$C$28,$T12))),0),CEILING(IF(설정!$C$26="원가 가산",$N12*(1+IF($T12="",설정!$C$28,$T12)),$N12/(1-IF($T12="",설정!$C$28,$T12))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V12" s="133">
+        <f>IF($N12="","",$N12*$G12)</f>
+        <v/>
+      </c>
+      <c r="W12" s="133">
+        <f>IF($P12="","",$P12*$G12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="171" t="n"/>
+      <c r="C13" s="171" t="n"/>
+      <c r="D13" s="172">
+        <f>IF($C13="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C13,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E13" s="173" t="n"/>
+      <c r="F13" s="133">
+        <f>IF($E13&lt;&gt;"",$E13,IF(N($D13)=0,"",$D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="174" t="n"/>
+      <c r="H13" s="133">
+        <f>IF($F13="","",$F13*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I13" s="132" t="n"/>
+      <c r="J13" s="132" t="n"/>
+      <c r="K13" s="133">
+        <f>IF($H13="","",IFERROR(IF(설정!$C$26="원가 가산",$H13*(1+IF($I13="",설정!$C$33,$I13)),$H13/(1-IF($I13="",설정!$C$33,$I13))),0))</f>
+        <v/>
+      </c>
+      <c r="L13" s="133">
+        <f>IF($H13="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K13*(1+IF($J13="",설정!$C$34,$J13)),$H13/(1-IF($I13="",설정!$C$33,$I13)-IF($J13="",설정!$C$34,$J13))),0),CEILING(IF(설정!$C$26="원가 가산",$K13*(1+IF($J13="",설정!$C$34,$J13)),$H13/(1-IF($I13="",설정!$C$33,$I13)-IF($J13="",설정!$C$34,$J13))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M13" s="175" t="n"/>
+      <c r="N13" s="133">
+        <f>IF($L13="","",IF($M13="",$L13,$M13))</f>
+        <v/>
+      </c>
+      <c r="O13" s="133">
+        <f>IF($N13="","",IF(설정!$C$26="원가 가산",$H13*IF($I13="",설정!$C$33,$I13),$N13*IF($I13="",설정!$C$33,$I13)))</f>
+        <v/>
+      </c>
+      <c r="P13" s="133">
+        <f>IF($N13="","",$N13-$H13-$O13)</f>
+        <v/>
+      </c>
+      <c r="Q13" s="176">
+        <f>IF(N($N13)=0,"",$P13/$N13)</f>
+        <v/>
+      </c>
+      <c r="R13" s="176">
+        <f>IF(N($L13)=0,"",$N13/$L13-1)</f>
+        <v/>
+      </c>
+      <c r="S13" s="176">
+        <f>IF(N($K13)=0,"",$N13/$K13-1)</f>
+        <v/>
+      </c>
+      <c r="T13" s="132" t="n"/>
+      <c r="U13" s="133">
+        <f>IF($N13="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N13*(1+IF($T13="",설정!$C$28,$T13)),$N13/(1-IF($T13="",설정!$C$28,$T13))),0),CEILING(IF(설정!$C$26="원가 가산",$N13*(1+IF($T13="",설정!$C$28,$T13)),$N13/(1-IF($T13="",설정!$C$28,$T13))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V13" s="133">
+        <f>IF($N13="","",$N13*$G13)</f>
+        <v/>
+      </c>
+      <c r="W13" s="133">
+        <f>IF($P13="","",$P13*$G13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="171" t="n"/>
+      <c r="C14" s="171" t="n"/>
+      <c r="D14" s="172">
+        <f>IF($C14="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C14,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E14" s="173" t="n"/>
+      <c r="F14" s="133">
+        <f>IF($E14&lt;&gt;"",$E14,IF(N($D14)=0,"",$D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="174" t="n"/>
+      <c r="H14" s="133">
+        <f>IF($F14="","",$F14*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I14" s="132" t="n"/>
+      <c r="J14" s="132" t="n"/>
+      <c r="K14" s="133">
+        <f>IF($H14="","",IFERROR(IF(설정!$C$26="원가 가산",$H14*(1+IF($I14="",설정!$C$33,$I14)),$H14/(1-IF($I14="",설정!$C$33,$I14))),0))</f>
+        <v/>
+      </c>
+      <c r="L14" s="133">
+        <f>IF($H14="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K14*(1+IF($J14="",설정!$C$34,$J14)),$H14/(1-IF($I14="",설정!$C$33,$I14)-IF($J14="",설정!$C$34,$J14))),0),CEILING(IF(설정!$C$26="원가 가산",$K14*(1+IF($J14="",설정!$C$34,$J14)),$H14/(1-IF($I14="",설정!$C$33,$I14)-IF($J14="",설정!$C$34,$J14))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M14" s="175" t="n"/>
+      <c r="N14" s="133">
+        <f>IF($L14="","",IF($M14="",$L14,$M14))</f>
+        <v/>
+      </c>
+      <c r="O14" s="133">
+        <f>IF($N14="","",IF(설정!$C$26="원가 가산",$H14*IF($I14="",설정!$C$33,$I14),$N14*IF($I14="",설정!$C$33,$I14)))</f>
+        <v/>
+      </c>
+      <c r="P14" s="133">
+        <f>IF($N14="","",$N14-$H14-$O14)</f>
+        <v/>
+      </c>
+      <c r="Q14" s="176">
+        <f>IF(N($N14)=0,"",$P14/$N14)</f>
+        <v/>
+      </c>
+      <c r="R14" s="176">
+        <f>IF(N($L14)=0,"",$N14/$L14-1)</f>
+        <v/>
+      </c>
+      <c r="S14" s="176">
+        <f>IF(N($K14)=0,"",$N14/$K14-1)</f>
+        <v/>
+      </c>
+      <c r="T14" s="132" t="n"/>
+      <c r="U14" s="133">
+        <f>IF($N14="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N14*(1+IF($T14="",설정!$C$28,$T14)),$N14/(1-IF($T14="",설정!$C$28,$T14))),0),CEILING(IF(설정!$C$26="원가 가산",$N14*(1+IF($T14="",설정!$C$28,$T14)),$N14/(1-IF($T14="",설정!$C$28,$T14))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V14" s="133">
+        <f>IF($N14="","",$N14*$G14)</f>
+        <v/>
+      </c>
+      <c r="W14" s="133">
+        <f>IF($P14="","",$P14*$G14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="171" t="n"/>
+      <c r="C15" s="171" t="n"/>
+      <c r="D15" s="172">
+        <f>IF($C15="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C15,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E15" s="173" t="n"/>
+      <c r="F15" s="133">
+        <f>IF($E15&lt;&gt;"",$E15,IF(N($D15)=0,"",$D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="174" t="n"/>
+      <c r="H15" s="133">
+        <f>IF($F15="","",$F15*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I15" s="132" t="n"/>
+      <c r="J15" s="132" t="n"/>
+      <c r="K15" s="133">
+        <f>IF($H15="","",IFERROR(IF(설정!$C$26="원가 가산",$H15*(1+IF($I15="",설정!$C$33,$I15)),$H15/(1-IF($I15="",설정!$C$33,$I15))),0))</f>
+        <v/>
+      </c>
+      <c r="L15" s="133">
+        <f>IF($H15="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K15*(1+IF($J15="",설정!$C$34,$J15)),$H15/(1-IF($I15="",설정!$C$33,$I15)-IF($J15="",설정!$C$34,$J15))),0),CEILING(IF(설정!$C$26="원가 가산",$K15*(1+IF($J15="",설정!$C$34,$J15)),$H15/(1-IF($I15="",설정!$C$33,$I15)-IF($J15="",설정!$C$34,$J15))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M15" s="175" t="n"/>
+      <c r="N15" s="133">
+        <f>IF($L15="","",IF($M15="",$L15,$M15))</f>
+        <v/>
+      </c>
+      <c r="O15" s="133">
+        <f>IF($N15="","",IF(설정!$C$26="원가 가산",$H15*IF($I15="",설정!$C$33,$I15),$N15*IF($I15="",설정!$C$33,$I15)))</f>
+        <v/>
+      </c>
+      <c r="P15" s="133">
+        <f>IF($N15="","",$N15-$H15-$O15)</f>
+        <v/>
+      </c>
+      <c r="Q15" s="176">
+        <f>IF(N($N15)=0,"",$P15/$N15)</f>
+        <v/>
+      </c>
+      <c r="R15" s="176">
+        <f>IF(N($L15)=0,"",$N15/$L15-1)</f>
+        <v/>
+      </c>
+      <c r="S15" s="176">
+        <f>IF(N($K15)=0,"",$N15/$K15-1)</f>
+        <v/>
+      </c>
+      <c r="T15" s="132" t="n"/>
+      <c r="U15" s="133">
+        <f>IF($N15="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N15*(1+IF($T15="",설정!$C$28,$T15)),$N15/(1-IF($T15="",설정!$C$28,$T15))),0),CEILING(IF(설정!$C$26="원가 가산",$N15*(1+IF($T15="",설정!$C$28,$T15)),$N15/(1-IF($T15="",설정!$C$28,$T15))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V15" s="133">
+        <f>IF($N15="","",$N15*$G15)</f>
+        <v/>
+      </c>
+      <c r="W15" s="133">
+        <f>IF($P15="","",$P15*$G15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="171" t="n"/>
+      <c r="C16" s="171" t="n"/>
+      <c r="D16" s="172">
+        <f>IF($C16="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C16,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E16" s="173" t="n"/>
+      <c r="F16" s="133">
+        <f>IF($E16&lt;&gt;"",$E16,IF(N($D16)=0,"",$D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="174" t="n"/>
+      <c r="H16" s="133">
+        <f>IF($F16="","",$F16*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I16" s="132" t="n"/>
+      <c r="J16" s="132" t="n"/>
+      <c r="K16" s="133">
+        <f>IF($H16="","",IFERROR(IF(설정!$C$26="원가 가산",$H16*(1+IF($I16="",설정!$C$33,$I16)),$H16/(1-IF($I16="",설정!$C$33,$I16))),0))</f>
+        <v/>
+      </c>
+      <c r="L16" s="133">
+        <f>IF($H16="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K16*(1+IF($J16="",설정!$C$34,$J16)),$H16/(1-IF($I16="",설정!$C$33,$I16)-IF($J16="",설정!$C$34,$J16))),0),CEILING(IF(설정!$C$26="원가 가산",$K16*(1+IF($J16="",설정!$C$34,$J16)),$H16/(1-IF($I16="",설정!$C$33,$I16)-IF($J16="",설정!$C$34,$J16))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M16" s="175" t="n"/>
+      <c r="N16" s="133">
+        <f>IF($L16="","",IF($M16="",$L16,$M16))</f>
+        <v/>
+      </c>
+      <c r="O16" s="133">
+        <f>IF($N16="","",IF(설정!$C$26="원가 가산",$H16*IF($I16="",설정!$C$33,$I16),$N16*IF($I16="",설정!$C$33,$I16)))</f>
+        <v/>
+      </c>
+      <c r="P16" s="133">
+        <f>IF($N16="","",$N16-$H16-$O16)</f>
+        <v/>
+      </c>
+      <c r="Q16" s="176">
+        <f>IF(N($N16)=0,"",$P16/$N16)</f>
+        <v/>
+      </c>
+      <c r="R16" s="176">
+        <f>IF(N($L16)=0,"",$N16/$L16-1)</f>
+        <v/>
+      </c>
+      <c r="S16" s="176">
+        <f>IF(N($K16)=0,"",$N16/$K16-1)</f>
+        <v/>
+      </c>
+      <c r="T16" s="132" t="n"/>
+      <c r="U16" s="133">
+        <f>IF($N16="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N16*(1+IF($T16="",설정!$C$28,$T16)),$N16/(1-IF($T16="",설정!$C$28,$T16))),0),CEILING(IF(설정!$C$26="원가 가산",$N16*(1+IF($T16="",설정!$C$28,$T16)),$N16/(1-IF($T16="",설정!$C$28,$T16))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V16" s="133">
+        <f>IF($N16="","",$N16*$G16)</f>
+        <v/>
+      </c>
+      <c r="W16" s="133">
+        <f>IF($P16="","",$P16*$G16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="171" t="n"/>
+      <c r="C17" s="171" t="n"/>
+      <c r="D17" s="172">
+        <f>IF($C17="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C17,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E17" s="173" t="n"/>
+      <c r="F17" s="133">
+        <f>IF($E17&lt;&gt;"",$E17,IF(N($D17)=0,"",$D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="174" t="n"/>
+      <c r="H17" s="133">
+        <f>IF($F17="","",$F17*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I17" s="132" t="n"/>
+      <c r="J17" s="132" t="n"/>
+      <c r="K17" s="133">
+        <f>IF($H17="","",IFERROR(IF(설정!$C$26="원가 가산",$H17*(1+IF($I17="",설정!$C$33,$I17)),$H17/(1-IF($I17="",설정!$C$33,$I17))),0))</f>
+        <v/>
+      </c>
+      <c r="L17" s="133">
+        <f>IF($H17="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K17*(1+IF($J17="",설정!$C$34,$J17)),$H17/(1-IF($I17="",설정!$C$33,$I17)-IF($J17="",설정!$C$34,$J17))),0),CEILING(IF(설정!$C$26="원가 가산",$K17*(1+IF($J17="",설정!$C$34,$J17)),$H17/(1-IF($I17="",설정!$C$33,$I17)-IF($J17="",설정!$C$34,$J17))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M17" s="175" t="n"/>
+      <c r="N17" s="133">
+        <f>IF($L17="","",IF($M17="",$L17,$M17))</f>
+        <v/>
+      </c>
+      <c r="O17" s="133">
+        <f>IF($N17="","",IF(설정!$C$26="원가 가산",$H17*IF($I17="",설정!$C$33,$I17),$N17*IF($I17="",설정!$C$33,$I17)))</f>
+        <v/>
+      </c>
+      <c r="P17" s="133">
+        <f>IF($N17="","",$N17-$H17-$O17)</f>
+        <v/>
+      </c>
+      <c r="Q17" s="176">
+        <f>IF(N($N17)=0,"",$P17/$N17)</f>
+        <v/>
+      </c>
+      <c r="R17" s="176">
+        <f>IF(N($L17)=0,"",$N17/$L17-1)</f>
+        <v/>
+      </c>
+      <c r="S17" s="176">
+        <f>IF(N($K17)=0,"",$N17/$K17-1)</f>
+        <v/>
+      </c>
+      <c r="T17" s="132" t="n"/>
+      <c r="U17" s="133">
+        <f>IF($N17="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N17*(1+IF($T17="",설정!$C$28,$T17)),$N17/(1-IF($T17="",설정!$C$28,$T17))),0),CEILING(IF(설정!$C$26="원가 가산",$N17*(1+IF($T17="",설정!$C$28,$T17)),$N17/(1-IF($T17="",설정!$C$28,$T17))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V17" s="133">
+        <f>IF($N17="","",$N17*$G17)</f>
+        <v/>
+      </c>
+      <c r="W17" s="133">
+        <f>IF($P17="","",$P17*$G17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="171" t="n"/>
+      <c r="C18" s="171" t="n"/>
+      <c r="D18" s="172">
+        <f>IF($C18="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C18,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E18" s="173" t="n"/>
+      <c r="F18" s="133">
+        <f>IF($E18&lt;&gt;"",$E18,IF(N($D18)=0,"",$D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="174" t="n"/>
+      <c r="H18" s="133">
+        <f>IF($F18="","",$F18*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I18" s="132" t="n"/>
+      <c r="J18" s="132" t="n"/>
+      <c r="K18" s="133">
+        <f>IF($H18="","",IFERROR(IF(설정!$C$26="원가 가산",$H18*(1+IF($I18="",설정!$C$33,$I18)),$H18/(1-IF($I18="",설정!$C$33,$I18))),0))</f>
+        <v/>
+      </c>
+      <c r="L18" s="133">
+        <f>IF($H18="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K18*(1+IF($J18="",설정!$C$34,$J18)),$H18/(1-IF($I18="",설정!$C$33,$I18)-IF($J18="",설정!$C$34,$J18))),0),CEILING(IF(설정!$C$26="원가 가산",$K18*(1+IF($J18="",설정!$C$34,$J18)),$H18/(1-IF($I18="",설정!$C$33,$I18)-IF($J18="",설정!$C$34,$J18))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M18" s="175" t="n"/>
+      <c r="N18" s="133">
+        <f>IF($L18="","",IF($M18="",$L18,$M18))</f>
+        <v/>
+      </c>
+      <c r="O18" s="133">
+        <f>IF($N18="","",IF(설정!$C$26="원가 가산",$H18*IF($I18="",설정!$C$33,$I18),$N18*IF($I18="",설정!$C$33,$I18)))</f>
+        <v/>
+      </c>
+      <c r="P18" s="133">
+        <f>IF($N18="","",$N18-$H18-$O18)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="176">
+        <f>IF(N($N18)=0,"",$P18/$N18)</f>
+        <v/>
+      </c>
+      <c r="R18" s="176">
+        <f>IF(N($L18)=0,"",$N18/$L18-1)</f>
+        <v/>
+      </c>
+      <c r="S18" s="176">
+        <f>IF(N($K18)=0,"",$N18/$K18-1)</f>
+        <v/>
+      </c>
+      <c r="T18" s="132" t="n"/>
+      <c r="U18" s="133">
+        <f>IF($N18="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N18*(1+IF($T18="",설정!$C$28,$T18)),$N18/(1-IF($T18="",설정!$C$28,$T18))),0),CEILING(IF(설정!$C$26="원가 가산",$N18*(1+IF($T18="",설정!$C$28,$T18)),$N18/(1-IF($T18="",설정!$C$28,$T18))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V18" s="133">
+        <f>IF($N18="","",$N18*$G18)</f>
+        <v/>
+      </c>
+      <c r="W18" s="133">
+        <f>IF($P18="","",$P18*$G18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="171" t="n"/>
+      <c r="C19" s="171" t="n"/>
+      <c r="D19" s="172">
+        <f>IF($C19="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C19,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E19" s="173" t="n"/>
+      <c r="F19" s="133">
+        <f>IF($E19&lt;&gt;"",$E19,IF(N($D19)=0,"",$D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="174" t="n"/>
+      <c r="H19" s="133">
+        <f>IF($F19="","",$F19*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I19" s="132" t="n"/>
+      <c r="J19" s="132" t="n"/>
+      <c r="K19" s="133">
+        <f>IF($H19="","",IFERROR(IF(설정!$C$26="원가 가산",$H19*(1+IF($I19="",설정!$C$33,$I19)),$H19/(1-IF($I19="",설정!$C$33,$I19))),0))</f>
+        <v/>
+      </c>
+      <c r="L19" s="133">
+        <f>IF($H19="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K19*(1+IF($J19="",설정!$C$34,$J19)),$H19/(1-IF($I19="",설정!$C$33,$I19)-IF($J19="",설정!$C$34,$J19))),0),CEILING(IF(설정!$C$26="원가 가산",$K19*(1+IF($J19="",설정!$C$34,$J19)),$H19/(1-IF($I19="",설정!$C$33,$I19)-IF($J19="",설정!$C$34,$J19))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M19" s="175" t="n"/>
+      <c r="N19" s="133">
+        <f>IF($L19="","",IF($M19="",$L19,$M19))</f>
+        <v/>
+      </c>
+      <c r="O19" s="133">
+        <f>IF($N19="","",IF(설정!$C$26="원가 가산",$H19*IF($I19="",설정!$C$33,$I19),$N19*IF($I19="",설정!$C$33,$I19)))</f>
+        <v/>
+      </c>
+      <c r="P19" s="133">
+        <f>IF($N19="","",$N19-$H19-$O19)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="176">
+        <f>IF(N($N19)=0,"",$P19/$N19)</f>
+        <v/>
+      </c>
+      <c r="R19" s="176">
+        <f>IF(N($L19)=0,"",$N19/$L19-1)</f>
+        <v/>
+      </c>
+      <c r="S19" s="176">
+        <f>IF(N($K19)=0,"",$N19/$K19-1)</f>
+        <v/>
+      </c>
+      <c r="T19" s="132" t="n"/>
+      <c r="U19" s="133">
+        <f>IF($N19="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N19*(1+IF($T19="",설정!$C$28,$T19)),$N19/(1-IF($T19="",설정!$C$28,$T19))),0),CEILING(IF(설정!$C$26="원가 가산",$N19*(1+IF($T19="",설정!$C$28,$T19)),$N19/(1-IF($T19="",설정!$C$28,$T19))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V19" s="133">
+        <f>IF($N19="","",$N19*$G19)</f>
+        <v/>
+      </c>
+      <c r="W19" s="133">
+        <f>IF($P19="","",$P19*$G19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="171" t="n"/>
+      <c r="C20" s="171" t="n"/>
+      <c r="D20" s="172">
+        <f>IF($C20="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C20,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E20" s="173" t="n"/>
+      <c r="F20" s="133">
+        <f>IF($E20&lt;&gt;"",$E20,IF(N($D20)=0,"",$D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="174" t="n"/>
+      <c r="H20" s="133">
+        <f>IF($F20="","",$F20*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I20" s="132" t="n"/>
+      <c r="J20" s="132" t="n"/>
+      <c r="K20" s="133">
+        <f>IF($H20="","",IFERROR(IF(설정!$C$26="원가 가산",$H20*(1+IF($I20="",설정!$C$33,$I20)),$H20/(1-IF($I20="",설정!$C$33,$I20))),0))</f>
+        <v/>
+      </c>
+      <c r="L20" s="133">
+        <f>IF($H20="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K20*(1+IF($J20="",설정!$C$34,$J20)),$H20/(1-IF($I20="",설정!$C$33,$I20)-IF($J20="",설정!$C$34,$J20))),0),CEILING(IF(설정!$C$26="원가 가산",$K20*(1+IF($J20="",설정!$C$34,$J20)),$H20/(1-IF($I20="",설정!$C$33,$I20)-IF($J20="",설정!$C$34,$J20))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M20" s="175" t="n"/>
+      <c r="N20" s="133">
+        <f>IF($L20="","",IF($M20="",$L20,$M20))</f>
+        <v/>
+      </c>
+      <c r="O20" s="133">
+        <f>IF($N20="","",IF(설정!$C$26="원가 가산",$H20*IF($I20="",설정!$C$33,$I20),$N20*IF($I20="",설정!$C$33,$I20)))</f>
+        <v/>
+      </c>
+      <c r="P20" s="133">
+        <f>IF($N20="","",$N20-$H20-$O20)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="176">
+        <f>IF(N($N20)=0,"",$P20/$N20)</f>
+        <v/>
+      </c>
+      <c r="R20" s="176">
+        <f>IF(N($L20)=0,"",$N20/$L20-1)</f>
+        <v/>
+      </c>
+      <c r="S20" s="176">
+        <f>IF(N($K20)=0,"",$N20/$K20-1)</f>
+        <v/>
+      </c>
+      <c r="T20" s="132" t="n"/>
+      <c r="U20" s="133">
+        <f>IF($N20="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N20*(1+IF($T20="",설정!$C$28,$T20)),$N20/(1-IF($T20="",설정!$C$28,$T20))),0),CEILING(IF(설정!$C$26="원가 가산",$N20*(1+IF($T20="",설정!$C$28,$T20)),$N20/(1-IF($T20="",설정!$C$28,$T20))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V20" s="133">
+        <f>IF($N20="","",$N20*$G20)</f>
+        <v/>
+      </c>
+      <c r="W20" s="133">
+        <f>IF($P20="","",$P20*$G20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="171" t="n"/>
+      <c r="C21" s="171" t="n"/>
+      <c r="D21" s="172">
+        <f>IF($C21="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C21,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E21" s="173" t="n"/>
+      <c r="F21" s="133">
+        <f>IF($E21&lt;&gt;"",$E21,IF(N($D21)=0,"",$D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="174" t="n"/>
+      <c r="H21" s="133">
+        <f>IF($F21="","",$F21*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I21" s="132" t="n"/>
+      <c r="J21" s="132" t="n"/>
+      <c r="K21" s="133">
+        <f>IF($H21="","",IFERROR(IF(설정!$C$26="원가 가산",$H21*(1+IF($I21="",설정!$C$33,$I21)),$H21/(1-IF($I21="",설정!$C$33,$I21))),0))</f>
+        <v/>
+      </c>
+      <c r="L21" s="133">
+        <f>IF($H21="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K21*(1+IF($J21="",설정!$C$34,$J21)),$H21/(1-IF($I21="",설정!$C$33,$I21)-IF($J21="",설정!$C$34,$J21))),0),CEILING(IF(설정!$C$26="원가 가산",$K21*(1+IF($J21="",설정!$C$34,$J21)),$H21/(1-IF($I21="",설정!$C$33,$I21)-IF($J21="",설정!$C$34,$J21))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M21" s="175" t="n"/>
+      <c r="N21" s="133">
+        <f>IF($L21="","",IF($M21="",$L21,$M21))</f>
+        <v/>
+      </c>
+      <c r="O21" s="133">
+        <f>IF($N21="","",IF(설정!$C$26="원가 가산",$H21*IF($I21="",설정!$C$33,$I21),$N21*IF($I21="",설정!$C$33,$I21)))</f>
+        <v/>
+      </c>
+      <c r="P21" s="133">
+        <f>IF($N21="","",$N21-$H21-$O21)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="176">
+        <f>IF(N($N21)=0,"",$P21/$N21)</f>
+        <v/>
+      </c>
+      <c r="R21" s="176">
+        <f>IF(N($L21)=0,"",$N21/$L21-1)</f>
+        <v/>
+      </c>
+      <c r="S21" s="176">
+        <f>IF(N($K21)=0,"",$N21/$K21-1)</f>
+        <v/>
+      </c>
+      <c r="T21" s="132" t="n"/>
+      <c r="U21" s="133">
+        <f>IF($N21="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N21*(1+IF($T21="",설정!$C$28,$T21)),$N21/(1-IF($T21="",설정!$C$28,$T21))),0),CEILING(IF(설정!$C$26="원가 가산",$N21*(1+IF($T21="",설정!$C$28,$T21)),$N21/(1-IF($T21="",설정!$C$28,$T21))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V21" s="133">
+        <f>IF($N21="","",$N21*$G21)</f>
+        <v/>
+      </c>
+      <c r="W21" s="133">
+        <f>IF($P21="","",$P21*$G21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="171" t="n"/>
+      <c r="C22" s="171" t="n"/>
+      <c r="D22" s="172">
+        <f>IF($C22="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C22,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E22" s="173" t="n"/>
+      <c r="F22" s="133">
+        <f>IF($E22&lt;&gt;"",$E22,IF(N($D22)=0,"",$D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="174" t="n"/>
+      <c r="H22" s="133">
+        <f>IF($F22="","",$F22*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I22" s="132" t="n"/>
+      <c r="J22" s="132" t="n"/>
+      <c r="K22" s="133">
+        <f>IF($H22="","",IFERROR(IF(설정!$C$26="원가 가산",$H22*(1+IF($I22="",설정!$C$33,$I22)),$H22/(1-IF($I22="",설정!$C$33,$I22))),0))</f>
+        <v/>
+      </c>
+      <c r="L22" s="133">
+        <f>IF($H22="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K22*(1+IF($J22="",설정!$C$34,$J22)),$H22/(1-IF($I22="",설정!$C$33,$I22)-IF($J22="",설정!$C$34,$J22))),0),CEILING(IF(설정!$C$26="원가 가산",$K22*(1+IF($J22="",설정!$C$34,$J22)),$H22/(1-IF($I22="",설정!$C$33,$I22)-IF($J22="",설정!$C$34,$J22))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M22" s="175" t="n"/>
+      <c r="N22" s="133">
+        <f>IF($L22="","",IF($M22="",$L22,$M22))</f>
+        <v/>
+      </c>
+      <c r="O22" s="133">
+        <f>IF($N22="","",IF(설정!$C$26="원가 가산",$H22*IF($I22="",설정!$C$33,$I22),$N22*IF($I22="",설정!$C$33,$I22)))</f>
+        <v/>
+      </c>
+      <c r="P22" s="133">
+        <f>IF($N22="","",$N22-$H22-$O22)</f>
+        <v/>
+      </c>
+      <c r="Q22" s="176">
+        <f>IF(N($N22)=0,"",$P22/$N22)</f>
+        <v/>
+      </c>
+      <c r="R22" s="176">
+        <f>IF(N($L22)=0,"",$N22/$L22-1)</f>
+        <v/>
+      </c>
+      <c r="S22" s="176">
+        <f>IF(N($K22)=0,"",$N22/$K22-1)</f>
+        <v/>
+      </c>
+      <c r="T22" s="132" t="n"/>
+      <c r="U22" s="133">
+        <f>IF($N22="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N22*(1+IF($T22="",설정!$C$28,$T22)),$N22/(1-IF($T22="",설정!$C$28,$T22))),0),CEILING(IF(설정!$C$26="원가 가산",$N22*(1+IF($T22="",설정!$C$28,$T22)),$N22/(1-IF($T22="",설정!$C$28,$T22))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V22" s="133">
+        <f>IF($N22="","",$N22*$G22)</f>
+        <v/>
+      </c>
+      <c r="W22" s="133">
+        <f>IF($P22="","",$P22*$G22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="171" t="n"/>
+      <c r="C23" s="171" t="n"/>
+      <c r="D23" s="172">
+        <f>IF($C23="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C23,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E23" s="173" t="n"/>
+      <c r="F23" s="133">
+        <f>IF($E23&lt;&gt;"",$E23,IF(N($D23)=0,"",$D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="174" t="n"/>
+      <c r="H23" s="133">
+        <f>IF($F23="","",$F23*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I23" s="132" t="n"/>
+      <c r="J23" s="132" t="n"/>
+      <c r="K23" s="133">
+        <f>IF($H23="","",IFERROR(IF(설정!$C$26="원가 가산",$H23*(1+IF($I23="",설정!$C$33,$I23)),$H23/(1-IF($I23="",설정!$C$33,$I23))),0))</f>
+        <v/>
+      </c>
+      <c r="L23" s="133">
+        <f>IF($H23="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K23*(1+IF($J23="",설정!$C$34,$J23)),$H23/(1-IF($I23="",설정!$C$33,$I23)-IF($J23="",설정!$C$34,$J23))),0),CEILING(IF(설정!$C$26="원가 가산",$K23*(1+IF($J23="",설정!$C$34,$J23)),$H23/(1-IF($I23="",설정!$C$33,$I23)-IF($J23="",설정!$C$34,$J23))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M23" s="175" t="n"/>
+      <c r="N23" s="133">
+        <f>IF($L23="","",IF($M23="",$L23,$M23))</f>
+        <v/>
+      </c>
+      <c r="O23" s="133">
+        <f>IF($N23="","",IF(설정!$C$26="원가 가산",$H23*IF($I23="",설정!$C$33,$I23),$N23*IF($I23="",설정!$C$33,$I23)))</f>
+        <v/>
+      </c>
+      <c r="P23" s="133">
+        <f>IF($N23="","",$N23-$H23-$O23)</f>
+        <v/>
+      </c>
+      <c r="Q23" s="176">
+        <f>IF(N($N23)=0,"",$P23/$N23)</f>
+        <v/>
+      </c>
+      <c r="R23" s="176">
+        <f>IF(N($L23)=0,"",$N23/$L23-1)</f>
+        <v/>
+      </c>
+      <c r="S23" s="176">
+        <f>IF(N($K23)=0,"",$N23/$K23-1)</f>
+        <v/>
+      </c>
+      <c r="T23" s="132" t="n"/>
+      <c r="U23" s="133">
+        <f>IF($N23="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N23*(1+IF($T23="",설정!$C$28,$T23)),$N23/(1-IF($T23="",설정!$C$28,$T23))),0),CEILING(IF(설정!$C$26="원가 가산",$N23*(1+IF($T23="",설정!$C$28,$T23)),$N23/(1-IF($T23="",설정!$C$28,$T23))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V23" s="133">
+        <f>IF($N23="","",$N23*$G23)</f>
+        <v/>
+      </c>
+      <c r="W23" s="133">
+        <f>IF($P23="","",$P23*$G23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="171" t="n"/>
+      <c r="C24" s="171" t="n"/>
+      <c r="D24" s="172">
+        <f>IF($C24="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C24,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E24" s="173" t="n"/>
+      <c r="F24" s="133">
+        <f>IF($E24&lt;&gt;"",$E24,IF(N($D24)=0,"",$D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="174" t="n"/>
+      <c r="H24" s="133">
+        <f>IF($F24="","",$F24*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I24" s="132" t="n"/>
+      <c r="J24" s="132" t="n"/>
+      <c r="K24" s="133">
+        <f>IF($H24="","",IFERROR(IF(설정!$C$26="원가 가산",$H24*(1+IF($I24="",설정!$C$33,$I24)),$H24/(1-IF($I24="",설정!$C$33,$I24))),0))</f>
+        <v/>
+      </c>
+      <c r="L24" s="133">
+        <f>IF($H24="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K24*(1+IF($J24="",설정!$C$34,$J24)),$H24/(1-IF($I24="",설정!$C$33,$I24)-IF($J24="",설정!$C$34,$J24))),0),CEILING(IF(설정!$C$26="원가 가산",$K24*(1+IF($J24="",설정!$C$34,$J24)),$H24/(1-IF($I24="",설정!$C$33,$I24)-IF($J24="",설정!$C$34,$J24))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M24" s="175" t="n"/>
+      <c r="N24" s="133">
+        <f>IF($L24="","",IF($M24="",$L24,$M24))</f>
+        <v/>
+      </c>
+      <c r="O24" s="133">
+        <f>IF($N24="","",IF(설정!$C$26="원가 가산",$H24*IF($I24="",설정!$C$33,$I24),$N24*IF($I24="",설정!$C$33,$I24)))</f>
+        <v/>
+      </c>
+      <c r="P24" s="133">
+        <f>IF($N24="","",$N24-$H24-$O24)</f>
+        <v/>
+      </c>
+      <c r="Q24" s="176">
+        <f>IF(N($N24)=0,"",$P24/$N24)</f>
+        <v/>
+      </c>
+      <c r="R24" s="176">
+        <f>IF(N($L24)=0,"",$N24/$L24-1)</f>
+        <v/>
+      </c>
+      <c r="S24" s="176">
+        <f>IF(N($K24)=0,"",$N24/$K24-1)</f>
+        <v/>
+      </c>
+      <c r="T24" s="132" t="n"/>
+      <c r="U24" s="133">
+        <f>IF($N24="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N24*(1+IF($T24="",설정!$C$28,$T24)),$N24/(1-IF($T24="",설정!$C$28,$T24))),0),CEILING(IF(설정!$C$26="원가 가산",$N24*(1+IF($T24="",설정!$C$28,$T24)),$N24/(1-IF($T24="",설정!$C$28,$T24))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V24" s="133">
+        <f>IF($N24="","",$N24*$G24)</f>
+        <v/>
+      </c>
+      <c r="W24" s="133">
+        <f>IF($P24="","",$P24*$G24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="171" t="n"/>
+      <c r="C25" s="171" t="n"/>
+      <c r="D25" s="172">
+        <f>IF($C25="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C25,자재판매가산출!$C$6:$C$24,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E25" s="173" t="n"/>
+      <c r="F25" s="133">
+        <f>IF($E25&lt;&gt;"",$E25,IF(N($D25)=0,"",$D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="174" t="n"/>
+      <c r="H25" s="133">
+        <f>IF($F25="","",$F25*(1+설정!$C$32))</f>
+        <v/>
+      </c>
+      <c r="I25" s="132" t="n"/>
+      <c r="J25" s="132" t="n"/>
+      <c r="K25" s="133">
+        <f>IF($H25="","",IFERROR(IF(설정!$C$26="원가 가산",$H25*(1+IF($I25="",설정!$C$33,$I25)),$H25/(1-IF($I25="",설정!$C$33,$I25))),0))</f>
+        <v/>
+      </c>
+      <c r="L25" s="133">
+        <f>IF($H25="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K25*(1+IF($J25="",설정!$C$34,$J25)),$H25/(1-IF($I25="",설정!$C$33,$I25)-IF($J25="",설정!$C$34,$J25))),0),CEILING(IF(설정!$C$26="원가 가산",$K25*(1+IF($J25="",설정!$C$34,$J25)),$H25/(1-IF($I25="",설정!$C$33,$I25)-IF($J25="",설정!$C$34,$J25))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="M25" s="175" t="n"/>
+      <c r="N25" s="133">
+        <f>IF($L25="","",IF($M25="",$L25,$M25))</f>
+        <v/>
+      </c>
+      <c r="O25" s="133">
+        <f>IF($N25="","",IF(설정!$C$26="원가 가산",$H25*IF($I25="",설정!$C$33,$I25),$N25*IF($I25="",설정!$C$33,$I25)))</f>
+        <v/>
+      </c>
+      <c r="P25" s="133">
+        <f>IF($N25="","",$N25-$H25-$O25)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="176">
+        <f>IF(N($N25)=0,"",$P25/$N25)</f>
+        <v/>
+      </c>
+      <c r="R25" s="176">
+        <f>IF(N($L25)=0,"",$N25/$L25-1)</f>
+        <v/>
+      </c>
+      <c r="S25" s="176">
+        <f>IF(N($K25)=0,"",$N25/$K25-1)</f>
+        <v/>
+      </c>
+      <c r="T25" s="132" t="n"/>
+      <c r="U25" s="133">
+        <f>IF($N25="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N25*(1+IF($T25="",설정!$C$28,$T25)),$N25/(1-IF($T25="",설정!$C$28,$T25))),0),CEILING(IF(설정!$C$26="원가 가산",$N25*(1+IF($T25="",설정!$C$28,$T25)),$N25/(1-IF($T25="",설정!$C$28,$T25))),설정!$C$27)),0))</f>
+        <v/>
+      </c>
+      <c r="V25" s="133">
+        <f>IF($N25="","",$N25*$G25)</f>
+        <v/>
+      </c>
+      <c r="W25" s="133">
+        <f>IF($P25="","",$P25*$G25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="147" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="C26" s="137" t="n"/>
+      <c r="D26" s="137" t="n"/>
+      <c r="E26" s="137" t="n"/>
+      <c r="F26" s="137" t="n"/>
+      <c r="G26" s="177">
+        <f>SUM(G6:G25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="137" t="n"/>
+      <c r="I26" s="137" t="n"/>
+      <c r="J26" s="137" t="n"/>
+      <c r="K26" s="137" t="n"/>
+      <c r="L26" s="137" t="n"/>
+      <c r="M26" s="137" t="n"/>
+      <c r="N26" s="137" t="n"/>
+      <c r="O26" s="137" t="n"/>
+      <c r="P26" s="137" t="n"/>
+      <c r="Q26" s="178">
+        <f>IFERROR(SUM(W6:W25)/SUM(V6:V25),0)</f>
+        <v/>
+      </c>
+      <c r="R26" s="137" t="n"/>
+      <c r="S26" s="137" t="n"/>
+      <c r="T26" s="137" t="n"/>
+      <c r="U26" s="137" t="n"/>
+      <c r="V26" s="179">
+        <f>SUM(V6:V25)</f>
+        <v/>
+      </c>
+      <c r="W26" s="179">
+        <f>SUM(W6:W25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="138" t="inlineStr">
+        <is>
+          <t>① 품목코드(C열)를 넣으면 자재판매가산출 시트에서 그 품목의 판매단가를 찾아 D열에 가져옵니다 — 그것이 태성 입고가입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="138" t="inlineStr">
+        <is>
+          <t>② D열이 비면 그 코드가 자재판매가산출에 없다는 뜻입니다. 그럴 때는 E열에 입고가를 직접 넣으세요. E열에 값이 있으면 조회값보다 우선합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="138" t="inlineStr">
+        <is>
+          <t>③ 태성 입고가가 곧 원가입니다. 입고 후 운반비 등이 붙으면 설정 C32(태성 추가비용률)에 넣으세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="138" t="inlineStr">
+        <is>
+          <t>④ 판관비율·영업이익률은 설정 C33·C34(태성 기준)를 씁니다. 플로우텍 상품 판매가의 값(C24·C25)과는 별개입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="138" t="inlineStr">
+        <is>
+          <t>⑤ L열 기준 판매가를 영업에 전달하고, 영업이 정한 값을 M열(노란 칸)에 적습니다. 비워 두면 기준가가 그대로 적용됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="139" t="inlineStr">
+        <is>
+          <t>⑥ 최종 판매가가 BEP 가격보다 낮으면 M열이 빨갛게 표시됩니다 — 팔수록 손해라는 뜻입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="138" t="inlineStr">
+        <is>
+          <t>표시 금액은 모두 부가세 별도입니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="M6:M25">
+    <cfRule type="expression" priority="1" dxfId="3" stopIfTrue="0">
+      <formula>AND(N($M6)&gt;0,N($K6)&gt;0,$M6&lt;$K6)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R6:R25">
+    <cfRule type="expression" priority="2" dxfId="4" stopIfTrue="0">
+      <formula>AND(N($N6)&gt;0,$N6&lt;$L6)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B4:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
@@ -4756,7 +6382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5914,7 +7540,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6324,13 +7950,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D35"/>
+  <dimension ref="B2:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="3.69921875" customWidth="1" min="1" max="1"/>
@@ -6698,57 +8324,112 @@
     <row r="31">
       <c r="B31" s="165" t="inlineStr">
         <is>
-          <t>■ 범례</t>
+          <t>■ 태성 재판매 (플로우텍 공급 → 태성 입고 → 재판매)</t>
         </is>
       </c>
       <c r="C31" s="138" t="n"/>
       <c r="D31" s="15" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="166" t="inlineStr">
-        <is>
-          <t>노란 채우기</t>
-        </is>
-      </c>
-      <c r="C32" s="138" t="inlineStr">
-        <is>
-          <t>반드시 확인하고 채워야 하는 칸</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="n"/>
+      <c r="B32" s="156" t="inlineStr">
+        <is>
+          <t>태성 추가비용률</t>
+        </is>
+      </c>
+      <c r="C32" s="157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="158" t="inlineStr">
+        <is>
+          <t>태성 입고 후 붙는 운반비 · 보관비 등. 없으면 0%.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1" thickBot="1">
-      <c r="B33" s="167" t="inlineStr">
-        <is>
-          <t>파란 글씨</t>
-        </is>
-      </c>
-      <c r="C33" s="168" t="inlineStr">
-        <is>
-          <t>직접 입력하는 칸</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="n"/>
+      <c r="B33" s="180" t="inlineStr">
+        <is>
+          <t>태성 판관비율</t>
+        </is>
+      </c>
+      <c r="C33" s="157" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="D33" s="181" t="inlineStr">
+        <is>
+          <t>태성 기준 판매관리비. 플로우텍 판관비(C24)와 별개로 관리합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="169" t="inlineStr">
         <is>
+          <t>태성 영업이익률</t>
+        </is>
+      </c>
+      <c r="C34" s="157" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D34" s="138" t="inlineStr">
+        <is>
+          <t>태성 기준 판매가에 얹을 목표 영업이익.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="162" t="n"/>
+      <c r="C35" s="138" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="182" t="inlineStr">
+        <is>
+          <t>■ 범례</t>
+        </is>
+      </c>
+      <c r="C37" s="138" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="183" t="inlineStr">
+        <is>
+          <t>노란 채우기</t>
+        </is>
+      </c>
+      <c r="C38" s="138" t="inlineStr">
+        <is>
+          <t>반드시 확인하고 채워야 하는 칸</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="184" t="inlineStr">
+        <is>
+          <t>파란 글씨</t>
+        </is>
+      </c>
+      <c r="C39" s="138" t="inlineStr">
+        <is>
+          <t>직접 입력하는 칸</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="169" t="inlineStr">
+        <is>
           <t>검정 글씨</t>
         </is>
       </c>
-      <c r="C34" s="138" t="inlineStr">
+      <c r="C40" s="138" t="inlineStr">
         <is>
           <t>수식 — 손대지 마세요</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="162" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="162" t="inlineStr">
         <is>
           <t>초록 글씨</t>
         </is>
       </c>
-      <c r="C35" s="138" t="inlineStr">
+      <c r="C41" s="138" t="inlineStr">
         <is>
           <t>다른 시트를 참조하는 수식</t>
         </is>
@@ -6771,7 +8452,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/수도명가 보급형 황동수전 판매단가.xlsx
+++ b/수도명가 보급형 황동수전 판매단가.xlsx
@@ -8,17 +8,16 @@
   <sheets>
     <sheet name="자재판매가산출" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="상품판매가산출" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="태성재판매가산출" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="유통가 보고" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="사용안내" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="설정" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="월평균환율" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="유통가 보고" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="사용안내" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="설정" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="월평균환율" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'유통가 보고'!$B$6:$K$26</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'유통가 보고'!$6:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'유통가 보고'!$B$2:$K$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'유통가 보고'!$B$6:$K$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'유통가 보고'!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'유통가 보고'!$B$2:$K$27</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -33,7 +32,7 @@
     <numFmt numFmtId="167" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="168" formatCode="#,##0;(#,##0);-"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="35">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -272,11 +271,6 @@
       <color rgb="0014606B"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -810,7 +804,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1079,28 +1073,13 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="33" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="28" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="28" fillId="8" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="31" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="30" fillId="10" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="30" fillId="10" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="30" fillId="10" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1"/>
     <cellStyle name="메모 2" xfId="2"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="맑은 고딕"/>
@@ -1146,13 +1125,6 @@
           <fgColor rgb="00FFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="맑은 고딕"/>
-        <color rgb="00C55A11"/>
-        <sz val="10"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1679,15 +1651,6 @@
 얹을 것이 없으므로 0%가 맞습니다.</t>
       </text>
     </comment>
-    <comment ref="C32" authorId="0" shapeId="0">
-      <text>
-        <t>태성 재판매가산출 시트에만 쓰입니다.
-태성 입고가(= 플로우텍 판매단가)가 곧 원가이므로
-추가 비용이 없으면 0%로 두세요.
-계산 방식(C26) · 절상 단위(C27) · 소비자 마진율(C28)은
-상품 판매가와 같은 값을 씁니다.</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -4628,1595 +4591,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:W34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="15" customWidth="1" min="23" max="23"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="170" t="inlineStr">
-        <is>
-          <t>태성 재판매가 산출 — 플로우텍 공급가를 원가로</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="162">
-        <f>"태성 입고가(= 플로우텍 판매단가) → 추가비용 "&amp;TEXT(설정!$C$32,"0.0%")&amp;" → 판관비 "&amp;TEXT(설정!$C$33,"0.0%")&amp;" → BEP 가격 → 영업이익 "&amp;TEXT(설정!$C$34,"0.0%")&amp;" → 기준 판매가 → (영업) 최종 판매가   ·   "&amp;설정!$C$26&amp;" 방식"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="B5" s="128" t="inlineStr">
-        <is>
-          <t>품목</t>
-        </is>
-      </c>
-      <c r="C5" s="128" t="inlineStr">
-        <is>
-          <t>품목코드</t>
-        </is>
-      </c>
-      <c r="D5" s="128" t="inlineStr">
-        <is>
-          <t>조회 입고가</t>
-        </is>
-      </c>
-      <c r="E5" s="128" t="inlineStr">
-        <is>
-          <t>입고가
-직접 입력</t>
-        </is>
-      </c>
-      <c r="F5" s="128" t="inlineStr">
-        <is>
-          <t>적용 입고가</t>
-        </is>
-      </c>
-      <c r="G5" s="128" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="H5" s="128" t="inlineStr">
-        <is>
-          <t>매입원가
-/개</t>
-        </is>
-      </c>
-      <c r="I5" s="128" t="inlineStr">
-        <is>
-          <t>판관비율</t>
-        </is>
-      </c>
-      <c r="J5" s="128" t="inlineStr">
-        <is>
-          <t>영업이익률</t>
-        </is>
-      </c>
-      <c r="K5" s="128" t="inlineStr">
-        <is>
-          <t>BEP 가격</t>
-        </is>
-      </c>
-      <c r="L5" s="128" t="inlineStr">
-        <is>
-          <t>기준 판매가</t>
-        </is>
-      </c>
-      <c r="M5" s="128" t="inlineStr">
-        <is>
-          <t>최종 판매가
-(영업 입력)</t>
-        </is>
-      </c>
-      <c r="N5" s="128" t="inlineStr">
-        <is>
-          <t>적용가</t>
-        </is>
-      </c>
-      <c r="O5" s="128" t="inlineStr">
-        <is>
-          <t>판관비
-/개</t>
-        </is>
-      </c>
-      <c r="P5" s="128" t="inlineStr">
-        <is>
-          <t>영업이익
-/개</t>
-        </is>
-      </c>
-      <c r="Q5" s="128" t="inlineStr">
-        <is>
-          <t>영업이익률
-(실제)</t>
-        </is>
-      </c>
-      <c r="R5" s="128" t="inlineStr">
-        <is>
-          <t>기준가 대비</t>
-        </is>
-      </c>
-      <c r="S5" s="128" t="inlineStr">
-        <is>
-          <t>BEP 대비</t>
-        </is>
-      </c>
-      <c r="T5" s="128" t="inlineStr">
-        <is>
-          <t>소비자
-마진율</t>
-        </is>
-      </c>
-      <c r="U5" s="128" t="inlineStr">
-        <is>
-          <t>소비자 판매가</t>
-        </is>
-      </c>
-      <c r="V5" s="128" t="inlineStr">
-        <is>
-          <t>매출 합계</t>
-        </is>
-      </c>
-      <c r="W5" s="128" t="inlineStr">
-        <is>
-          <t>영업이익 합계</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="171" t="n"/>
-      <c r="C6" s="171" t="n"/>
-      <c r="D6" s="172">
-        <f>IF($C6="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C6,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E6" s="173" t="n"/>
-      <c r="F6" s="133">
-        <f>IF($E6&lt;&gt;"",$E6,IF(N($D6)=0,"",$D6))</f>
-        <v/>
-      </c>
-      <c r="G6" s="174" t="n"/>
-      <c r="H6" s="133">
-        <f>IF($F6="","",$F6*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I6" s="132" t="n"/>
-      <c r="J6" s="132" t="n"/>
-      <c r="K6" s="133">
-        <f>IF($H6="","",IFERROR(IF(설정!$C$26="원가 가산",$H6*(1+IF($I6="",설정!$C$33,$I6)),$H6/(1-IF($I6="",설정!$C$33,$I6))),0))</f>
-        <v/>
-      </c>
-      <c r="L6" s="133">
-        <f>IF($H6="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K6*(1+IF($J6="",설정!$C$34,$J6)),$H6/(1-IF($I6="",설정!$C$33,$I6)-IF($J6="",설정!$C$34,$J6))),0),CEILING(IF(설정!$C$26="원가 가산",$K6*(1+IF($J6="",설정!$C$34,$J6)),$H6/(1-IF($I6="",설정!$C$33,$I6)-IF($J6="",설정!$C$34,$J6))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M6" s="175" t="n"/>
-      <c r="N6" s="133">
-        <f>IF($L6="","",IF($M6="",$L6,$M6))</f>
-        <v/>
-      </c>
-      <c r="O6" s="133">
-        <f>IF($N6="","",IF(설정!$C$26="원가 가산",$H6*IF($I6="",설정!$C$33,$I6),$N6*IF($I6="",설정!$C$33,$I6)))</f>
-        <v/>
-      </c>
-      <c r="P6" s="133">
-        <f>IF($N6="","",$N6-$H6-$O6)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="176">
-        <f>IF(N($N6)=0,"",$P6/$N6)</f>
-        <v/>
-      </c>
-      <c r="R6" s="176">
-        <f>IF(N($L6)=0,"",$N6/$L6-1)</f>
-        <v/>
-      </c>
-      <c r="S6" s="176">
-        <f>IF(N($K6)=0,"",$N6/$K6-1)</f>
-        <v/>
-      </c>
-      <c r="T6" s="132" t="n"/>
-      <c r="U6" s="133">
-        <f>IF($N6="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N6*(1+IF($T6="",설정!$C$28,$T6)),$N6/(1-IF($T6="",설정!$C$28,$T6))),0),CEILING(IF(설정!$C$26="원가 가산",$N6*(1+IF($T6="",설정!$C$28,$T6)),$N6/(1-IF($T6="",설정!$C$28,$T6))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V6" s="133">
-        <f>IF($N6="","",$N6*$G6)</f>
-        <v/>
-      </c>
-      <c r="W6" s="133">
-        <f>IF($P6="","",$P6*$G6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="171" t="n"/>
-      <c r="C7" s="171" t="n"/>
-      <c r="D7" s="172">
-        <f>IF($C7="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C7,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E7" s="173" t="n"/>
-      <c r="F7" s="133">
-        <f>IF($E7&lt;&gt;"",$E7,IF(N($D7)=0,"",$D7))</f>
-        <v/>
-      </c>
-      <c r="G7" s="174" t="n"/>
-      <c r="H7" s="133">
-        <f>IF($F7="","",$F7*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I7" s="132" t="n"/>
-      <c r="J7" s="132" t="n"/>
-      <c r="K7" s="133">
-        <f>IF($H7="","",IFERROR(IF(설정!$C$26="원가 가산",$H7*(1+IF($I7="",설정!$C$33,$I7)),$H7/(1-IF($I7="",설정!$C$33,$I7))),0))</f>
-        <v/>
-      </c>
-      <c r="L7" s="133">
-        <f>IF($H7="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K7*(1+IF($J7="",설정!$C$34,$J7)),$H7/(1-IF($I7="",설정!$C$33,$I7)-IF($J7="",설정!$C$34,$J7))),0),CEILING(IF(설정!$C$26="원가 가산",$K7*(1+IF($J7="",설정!$C$34,$J7)),$H7/(1-IF($I7="",설정!$C$33,$I7)-IF($J7="",설정!$C$34,$J7))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M7" s="175" t="n"/>
-      <c r="N7" s="133">
-        <f>IF($L7="","",IF($M7="",$L7,$M7))</f>
-        <v/>
-      </c>
-      <c r="O7" s="133">
-        <f>IF($N7="","",IF(설정!$C$26="원가 가산",$H7*IF($I7="",설정!$C$33,$I7),$N7*IF($I7="",설정!$C$33,$I7)))</f>
-        <v/>
-      </c>
-      <c r="P7" s="133">
-        <f>IF($N7="","",$N7-$H7-$O7)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="176">
-        <f>IF(N($N7)=0,"",$P7/$N7)</f>
-        <v/>
-      </c>
-      <c r="R7" s="176">
-        <f>IF(N($L7)=0,"",$N7/$L7-1)</f>
-        <v/>
-      </c>
-      <c r="S7" s="176">
-        <f>IF(N($K7)=0,"",$N7/$K7-1)</f>
-        <v/>
-      </c>
-      <c r="T7" s="132" t="n"/>
-      <c r="U7" s="133">
-        <f>IF($N7="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N7*(1+IF($T7="",설정!$C$28,$T7)),$N7/(1-IF($T7="",설정!$C$28,$T7))),0),CEILING(IF(설정!$C$26="원가 가산",$N7*(1+IF($T7="",설정!$C$28,$T7)),$N7/(1-IF($T7="",설정!$C$28,$T7))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V7" s="133">
-        <f>IF($N7="","",$N7*$G7)</f>
-        <v/>
-      </c>
-      <c r="W7" s="133">
-        <f>IF($P7="","",$P7*$G7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="171" t="n"/>
-      <c r="C8" s="171" t="n"/>
-      <c r="D8" s="172">
-        <f>IF($C8="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C8,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E8" s="173" t="n"/>
-      <c r="F8" s="133">
-        <f>IF($E8&lt;&gt;"",$E8,IF(N($D8)=0,"",$D8))</f>
-        <v/>
-      </c>
-      <c r="G8" s="174" t="n"/>
-      <c r="H8" s="133">
-        <f>IF($F8="","",$F8*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I8" s="132" t="n"/>
-      <c r="J8" s="132" t="n"/>
-      <c r="K8" s="133">
-        <f>IF($H8="","",IFERROR(IF(설정!$C$26="원가 가산",$H8*(1+IF($I8="",설정!$C$33,$I8)),$H8/(1-IF($I8="",설정!$C$33,$I8))),0))</f>
-        <v/>
-      </c>
-      <c r="L8" s="133">
-        <f>IF($H8="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K8*(1+IF($J8="",설정!$C$34,$J8)),$H8/(1-IF($I8="",설정!$C$33,$I8)-IF($J8="",설정!$C$34,$J8))),0),CEILING(IF(설정!$C$26="원가 가산",$K8*(1+IF($J8="",설정!$C$34,$J8)),$H8/(1-IF($I8="",설정!$C$33,$I8)-IF($J8="",설정!$C$34,$J8))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M8" s="175" t="n"/>
-      <c r="N8" s="133">
-        <f>IF($L8="","",IF($M8="",$L8,$M8))</f>
-        <v/>
-      </c>
-      <c r="O8" s="133">
-        <f>IF($N8="","",IF(설정!$C$26="원가 가산",$H8*IF($I8="",설정!$C$33,$I8),$N8*IF($I8="",설정!$C$33,$I8)))</f>
-        <v/>
-      </c>
-      <c r="P8" s="133">
-        <f>IF($N8="","",$N8-$H8-$O8)</f>
-        <v/>
-      </c>
-      <c r="Q8" s="176">
-        <f>IF(N($N8)=0,"",$P8/$N8)</f>
-        <v/>
-      </c>
-      <c r="R8" s="176">
-        <f>IF(N($L8)=0,"",$N8/$L8-1)</f>
-        <v/>
-      </c>
-      <c r="S8" s="176">
-        <f>IF(N($K8)=0,"",$N8/$K8-1)</f>
-        <v/>
-      </c>
-      <c r="T8" s="132" t="n"/>
-      <c r="U8" s="133">
-        <f>IF($N8="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N8*(1+IF($T8="",설정!$C$28,$T8)),$N8/(1-IF($T8="",설정!$C$28,$T8))),0),CEILING(IF(설정!$C$26="원가 가산",$N8*(1+IF($T8="",설정!$C$28,$T8)),$N8/(1-IF($T8="",설정!$C$28,$T8))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V8" s="133">
-        <f>IF($N8="","",$N8*$G8)</f>
-        <v/>
-      </c>
-      <c r="W8" s="133">
-        <f>IF($P8="","",$P8*$G8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="171" t="n"/>
-      <c r="C9" s="171" t="n"/>
-      <c r="D9" s="172">
-        <f>IF($C9="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C9,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E9" s="173" t="n"/>
-      <c r="F9" s="133">
-        <f>IF($E9&lt;&gt;"",$E9,IF(N($D9)=0,"",$D9))</f>
-        <v/>
-      </c>
-      <c r="G9" s="174" t="n"/>
-      <c r="H9" s="133">
-        <f>IF($F9="","",$F9*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I9" s="132" t="n"/>
-      <c r="J9" s="132" t="n"/>
-      <c r="K9" s="133">
-        <f>IF($H9="","",IFERROR(IF(설정!$C$26="원가 가산",$H9*(1+IF($I9="",설정!$C$33,$I9)),$H9/(1-IF($I9="",설정!$C$33,$I9))),0))</f>
-        <v/>
-      </c>
-      <c r="L9" s="133">
-        <f>IF($H9="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K9*(1+IF($J9="",설정!$C$34,$J9)),$H9/(1-IF($I9="",설정!$C$33,$I9)-IF($J9="",설정!$C$34,$J9))),0),CEILING(IF(설정!$C$26="원가 가산",$K9*(1+IF($J9="",설정!$C$34,$J9)),$H9/(1-IF($I9="",설정!$C$33,$I9)-IF($J9="",설정!$C$34,$J9))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M9" s="175" t="n"/>
-      <c r="N9" s="133">
-        <f>IF($L9="","",IF($M9="",$L9,$M9))</f>
-        <v/>
-      </c>
-      <c r="O9" s="133">
-        <f>IF($N9="","",IF(설정!$C$26="원가 가산",$H9*IF($I9="",설정!$C$33,$I9),$N9*IF($I9="",설정!$C$33,$I9)))</f>
-        <v/>
-      </c>
-      <c r="P9" s="133">
-        <f>IF($N9="","",$N9-$H9-$O9)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="176">
-        <f>IF(N($N9)=0,"",$P9/$N9)</f>
-        <v/>
-      </c>
-      <c r="R9" s="176">
-        <f>IF(N($L9)=0,"",$N9/$L9-1)</f>
-        <v/>
-      </c>
-      <c r="S9" s="176">
-        <f>IF(N($K9)=0,"",$N9/$K9-1)</f>
-        <v/>
-      </c>
-      <c r="T9" s="132" t="n"/>
-      <c r="U9" s="133">
-        <f>IF($N9="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N9*(1+IF($T9="",설정!$C$28,$T9)),$N9/(1-IF($T9="",설정!$C$28,$T9))),0),CEILING(IF(설정!$C$26="원가 가산",$N9*(1+IF($T9="",설정!$C$28,$T9)),$N9/(1-IF($T9="",설정!$C$28,$T9))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V9" s="133">
-        <f>IF($N9="","",$N9*$G9)</f>
-        <v/>
-      </c>
-      <c r="W9" s="133">
-        <f>IF($P9="","",$P9*$G9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="171" t="n"/>
-      <c r="C10" s="171" t="n"/>
-      <c r="D10" s="172">
-        <f>IF($C10="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C10,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E10" s="173" t="n"/>
-      <c r="F10" s="133">
-        <f>IF($E10&lt;&gt;"",$E10,IF(N($D10)=0,"",$D10))</f>
-        <v/>
-      </c>
-      <c r="G10" s="174" t="n"/>
-      <c r="H10" s="133">
-        <f>IF($F10="","",$F10*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I10" s="132" t="n"/>
-      <c r="J10" s="132" t="n"/>
-      <c r="K10" s="133">
-        <f>IF($H10="","",IFERROR(IF(설정!$C$26="원가 가산",$H10*(1+IF($I10="",설정!$C$33,$I10)),$H10/(1-IF($I10="",설정!$C$33,$I10))),0))</f>
-        <v/>
-      </c>
-      <c r="L10" s="133">
-        <f>IF($H10="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K10*(1+IF($J10="",설정!$C$34,$J10)),$H10/(1-IF($I10="",설정!$C$33,$I10)-IF($J10="",설정!$C$34,$J10))),0),CEILING(IF(설정!$C$26="원가 가산",$K10*(1+IF($J10="",설정!$C$34,$J10)),$H10/(1-IF($I10="",설정!$C$33,$I10)-IF($J10="",설정!$C$34,$J10))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M10" s="175" t="n"/>
-      <c r="N10" s="133">
-        <f>IF($L10="","",IF($M10="",$L10,$M10))</f>
-        <v/>
-      </c>
-      <c r="O10" s="133">
-        <f>IF($N10="","",IF(설정!$C$26="원가 가산",$H10*IF($I10="",설정!$C$33,$I10),$N10*IF($I10="",설정!$C$33,$I10)))</f>
-        <v/>
-      </c>
-      <c r="P10" s="133">
-        <f>IF($N10="","",$N10-$H10-$O10)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="176">
-        <f>IF(N($N10)=0,"",$P10/$N10)</f>
-        <v/>
-      </c>
-      <c r="R10" s="176">
-        <f>IF(N($L10)=0,"",$N10/$L10-1)</f>
-        <v/>
-      </c>
-      <c r="S10" s="176">
-        <f>IF(N($K10)=0,"",$N10/$K10-1)</f>
-        <v/>
-      </c>
-      <c r="T10" s="132" t="n"/>
-      <c r="U10" s="133">
-        <f>IF($N10="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N10*(1+IF($T10="",설정!$C$28,$T10)),$N10/(1-IF($T10="",설정!$C$28,$T10))),0),CEILING(IF(설정!$C$26="원가 가산",$N10*(1+IF($T10="",설정!$C$28,$T10)),$N10/(1-IF($T10="",설정!$C$28,$T10))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V10" s="133">
-        <f>IF($N10="","",$N10*$G10)</f>
-        <v/>
-      </c>
-      <c r="W10" s="133">
-        <f>IF($P10="","",$P10*$G10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="171" t="n"/>
-      <c r="C11" s="171" t="n"/>
-      <c r="D11" s="172">
-        <f>IF($C11="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C11,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E11" s="173" t="n"/>
-      <c r="F11" s="133">
-        <f>IF($E11&lt;&gt;"",$E11,IF(N($D11)=0,"",$D11))</f>
-        <v/>
-      </c>
-      <c r="G11" s="174" t="n"/>
-      <c r="H11" s="133">
-        <f>IF($F11="","",$F11*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I11" s="132" t="n"/>
-      <c r="J11" s="132" t="n"/>
-      <c r="K11" s="133">
-        <f>IF($H11="","",IFERROR(IF(설정!$C$26="원가 가산",$H11*(1+IF($I11="",설정!$C$33,$I11)),$H11/(1-IF($I11="",설정!$C$33,$I11))),0))</f>
-        <v/>
-      </c>
-      <c r="L11" s="133">
-        <f>IF($H11="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K11*(1+IF($J11="",설정!$C$34,$J11)),$H11/(1-IF($I11="",설정!$C$33,$I11)-IF($J11="",설정!$C$34,$J11))),0),CEILING(IF(설정!$C$26="원가 가산",$K11*(1+IF($J11="",설정!$C$34,$J11)),$H11/(1-IF($I11="",설정!$C$33,$I11)-IF($J11="",설정!$C$34,$J11))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M11" s="175" t="n"/>
-      <c r="N11" s="133">
-        <f>IF($L11="","",IF($M11="",$L11,$M11))</f>
-        <v/>
-      </c>
-      <c r="O11" s="133">
-        <f>IF($N11="","",IF(설정!$C$26="원가 가산",$H11*IF($I11="",설정!$C$33,$I11),$N11*IF($I11="",설정!$C$33,$I11)))</f>
-        <v/>
-      </c>
-      <c r="P11" s="133">
-        <f>IF($N11="","",$N11-$H11-$O11)</f>
-        <v/>
-      </c>
-      <c r="Q11" s="176">
-        <f>IF(N($N11)=0,"",$P11/$N11)</f>
-        <v/>
-      </c>
-      <c r="R11" s="176">
-        <f>IF(N($L11)=0,"",$N11/$L11-1)</f>
-        <v/>
-      </c>
-      <c r="S11" s="176">
-        <f>IF(N($K11)=0,"",$N11/$K11-1)</f>
-        <v/>
-      </c>
-      <c r="T11" s="132" t="n"/>
-      <c r="U11" s="133">
-        <f>IF($N11="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N11*(1+IF($T11="",설정!$C$28,$T11)),$N11/(1-IF($T11="",설정!$C$28,$T11))),0),CEILING(IF(설정!$C$26="원가 가산",$N11*(1+IF($T11="",설정!$C$28,$T11)),$N11/(1-IF($T11="",설정!$C$28,$T11))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V11" s="133">
-        <f>IF($N11="","",$N11*$G11)</f>
-        <v/>
-      </c>
-      <c r="W11" s="133">
-        <f>IF($P11="","",$P11*$G11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="171" t="n"/>
-      <c r="C12" s="171" t="n"/>
-      <c r="D12" s="172">
-        <f>IF($C12="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C12,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E12" s="173" t="n"/>
-      <c r="F12" s="133">
-        <f>IF($E12&lt;&gt;"",$E12,IF(N($D12)=0,"",$D12))</f>
-        <v/>
-      </c>
-      <c r="G12" s="174" t="n"/>
-      <c r="H12" s="133">
-        <f>IF($F12="","",$F12*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I12" s="132" t="n"/>
-      <c r="J12" s="132" t="n"/>
-      <c r="K12" s="133">
-        <f>IF($H12="","",IFERROR(IF(설정!$C$26="원가 가산",$H12*(1+IF($I12="",설정!$C$33,$I12)),$H12/(1-IF($I12="",설정!$C$33,$I12))),0))</f>
-        <v/>
-      </c>
-      <c r="L12" s="133">
-        <f>IF($H12="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K12*(1+IF($J12="",설정!$C$34,$J12)),$H12/(1-IF($I12="",설정!$C$33,$I12)-IF($J12="",설정!$C$34,$J12))),0),CEILING(IF(설정!$C$26="원가 가산",$K12*(1+IF($J12="",설정!$C$34,$J12)),$H12/(1-IF($I12="",설정!$C$33,$I12)-IF($J12="",설정!$C$34,$J12))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M12" s="175" t="n"/>
-      <c r="N12" s="133">
-        <f>IF($L12="","",IF($M12="",$L12,$M12))</f>
-        <v/>
-      </c>
-      <c r="O12" s="133">
-        <f>IF($N12="","",IF(설정!$C$26="원가 가산",$H12*IF($I12="",설정!$C$33,$I12),$N12*IF($I12="",설정!$C$33,$I12)))</f>
-        <v/>
-      </c>
-      <c r="P12" s="133">
-        <f>IF($N12="","",$N12-$H12-$O12)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="176">
-        <f>IF(N($N12)=0,"",$P12/$N12)</f>
-        <v/>
-      </c>
-      <c r="R12" s="176">
-        <f>IF(N($L12)=0,"",$N12/$L12-1)</f>
-        <v/>
-      </c>
-      <c r="S12" s="176">
-        <f>IF(N($K12)=0,"",$N12/$K12-1)</f>
-        <v/>
-      </c>
-      <c r="T12" s="132" t="n"/>
-      <c r="U12" s="133">
-        <f>IF($N12="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N12*(1+IF($T12="",설정!$C$28,$T12)),$N12/(1-IF($T12="",설정!$C$28,$T12))),0),CEILING(IF(설정!$C$26="원가 가산",$N12*(1+IF($T12="",설정!$C$28,$T12)),$N12/(1-IF($T12="",설정!$C$28,$T12))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V12" s="133">
-        <f>IF($N12="","",$N12*$G12)</f>
-        <v/>
-      </c>
-      <c r="W12" s="133">
-        <f>IF($P12="","",$P12*$G12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="171" t="n"/>
-      <c r="C13" s="171" t="n"/>
-      <c r="D13" s="172">
-        <f>IF($C13="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C13,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E13" s="173" t="n"/>
-      <c r="F13" s="133">
-        <f>IF($E13&lt;&gt;"",$E13,IF(N($D13)=0,"",$D13))</f>
-        <v/>
-      </c>
-      <c r="G13" s="174" t="n"/>
-      <c r="H13" s="133">
-        <f>IF($F13="","",$F13*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I13" s="132" t="n"/>
-      <c r="J13" s="132" t="n"/>
-      <c r="K13" s="133">
-        <f>IF($H13="","",IFERROR(IF(설정!$C$26="원가 가산",$H13*(1+IF($I13="",설정!$C$33,$I13)),$H13/(1-IF($I13="",설정!$C$33,$I13))),0))</f>
-        <v/>
-      </c>
-      <c r="L13" s="133">
-        <f>IF($H13="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K13*(1+IF($J13="",설정!$C$34,$J13)),$H13/(1-IF($I13="",설정!$C$33,$I13)-IF($J13="",설정!$C$34,$J13))),0),CEILING(IF(설정!$C$26="원가 가산",$K13*(1+IF($J13="",설정!$C$34,$J13)),$H13/(1-IF($I13="",설정!$C$33,$I13)-IF($J13="",설정!$C$34,$J13))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M13" s="175" t="n"/>
-      <c r="N13" s="133">
-        <f>IF($L13="","",IF($M13="",$L13,$M13))</f>
-        <v/>
-      </c>
-      <c r="O13" s="133">
-        <f>IF($N13="","",IF(설정!$C$26="원가 가산",$H13*IF($I13="",설정!$C$33,$I13),$N13*IF($I13="",설정!$C$33,$I13)))</f>
-        <v/>
-      </c>
-      <c r="P13" s="133">
-        <f>IF($N13="","",$N13-$H13-$O13)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="176">
-        <f>IF(N($N13)=0,"",$P13/$N13)</f>
-        <v/>
-      </c>
-      <c r="R13" s="176">
-        <f>IF(N($L13)=0,"",$N13/$L13-1)</f>
-        <v/>
-      </c>
-      <c r="S13" s="176">
-        <f>IF(N($K13)=0,"",$N13/$K13-1)</f>
-        <v/>
-      </c>
-      <c r="T13" s="132" t="n"/>
-      <c r="U13" s="133">
-        <f>IF($N13="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N13*(1+IF($T13="",설정!$C$28,$T13)),$N13/(1-IF($T13="",설정!$C$28,$T13))),0),CEILING(IF(설정!$C$26="원가 가산",$N13*(1+IF($T13="",설정!$C$28,$T13)),$N13/(1-IF($T13="",설정!$C$28,$T13))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V13" s="133">
-        <f>IF($N13="","",$N13*$G13)</f>
-        <v/>
-      </c>
-      <c r="W13" s="133">
-        <f>IF($P13="","",$P13*$G13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="171" t="n"/>
-      <c r="C14" s="171" t="n"/>
-      <c r="D14" s="172">
-        <f>IF($C14="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C14,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E14" s="173" t="n"/>
-      <c r="F14" s="133">
-        <f>IF($E14&lt;&gt;"",$E14,IF(N($D14)=0,"",$D14))</f>
-        <v/>
-      </c>
-      <c r="G14" s="174" t="n"/>
-      <c r="H14" s="133">
-        <f>IF($F14="","",$F14*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I14" s="132" t="n"/>
-      <c r="J14" s="132" t="n"/>
-      <c r="K14" s="133">
-        <f>IF($H14="","",IFERROR(IF(설정!$C$26="원가 가산",$H14*(1+IF($I14="",설정!$C$33,$I14)),$H14/(1-IF($I14="",설정!$C$33,$I14))),0))</f>
-        <v/>
-      </c>
-      <c r="L14" s="133">
-        <f>IF($H14="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K14*(1+IF($J14="",설정!$C$34,$J14)),$H14/(1-IF($I14="",설정!$C$33,$I14)-IF($J14="",설정!$C$34,$J14))),0),CEILING(IF(설정!$C$26="원가 가산",$K14*(1+IF($J14="",설정!$C$34,$J14)),$H14/(1-IF($I14="",설정!$C$33,$I14)-IF($J14="",설정!$C$34,$J14))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M14" s="175" t="n"/>
-      <c r="N14" s="133">
-        <f>IF($L14="","",IF($M14="",$L14,$M14))</f>
-        <v/>
-      </c>
-      <c r="O14" s="133">
-        <f>IF($N14="","",IF(설정!$C$26="원가 가산",$H14*IF($I14="",설정!$C$33,$I14),$N14*IF($I14="",설정!$C$33,$I14)))</f>
-        <v/>
-      </c>
-      <c r="P14" s="133">
-        <f>IF($N14="","",$N14-$H14-$O14)</f>
-        <v/>
-      </c>
-      <c r="Q14" s="176">
-        <f>IF(N($N14)=0,"",$P14/$N14)</f>
-        <v/>
-      </c>
-      <c r="R14" s="176">
-        <f>IF(N($L14)=0,"",$N14/$L14-1)</f>
-        <v/>
-      </c>
-      <c r="S14" s="176">
-        <f>IF(N($K14)=0,"",$N14/$K14-1)</f>
-        <v/>
-      </c>
-      <c r="T14" s="132" t="n"/>
-      <c r="U14" s="133">
-        <f>IF($N14="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N14*(1+IF($T14="",설정!$C$28,$T14)),$N14/(1-IF($T14="",설정!$C$28,$T14))),0),CEILING(IF(설정!$C$26="원가 가산",$N14*(1+IF($T14="",설정!$C$28,$T14)),$N14/(1-IF($T14="",설정!$C$28,$T14))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V14" s="133">
-        <f>IF($N14="","",$N14*$G14)</f>
-        <v/>
-      </c>
-      <c r="W14" s="133">
-        <f>IF($P14="","",$P14*$G14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="171" t="n"/>
-      <c r="C15" s="171" t="n"/>
-      <c r="D15" s="172">
-        <f>IF($C15="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C15,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E15" s="173" t="n"/>
-      <c r="F15" s="133">
-        <f>IF($E15&lt;&gt;"",$E15,IF(N($D15)=0,"",$D15))</f>
-        <v/>
-      </c>
-      <c r="G15" s="174" t="n"/>
-      <c r="H15" s="133">
-        <f>IF($F15="","",$F15*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I15" s="132" t="n"/>
-      <c r="J15" s="132" t="n"/>
-      <c r="K15" s="133">
-        <f>IF($H15="","",IFERROR(IF(설정!$C$26="원가 가산",$H15*(1+IF($I15="",설정!$C$33,$I15)),$H15/(1-IF($I15="",설정!$C$33,$I15))),0))</f>
-        <v/>
-      </c>
-      <c r="L15" s="133">
-        <f>IF($H15="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K15*(1+IF($J15="",설정!$C$34,$J15)),$H15/(1-IF($I15="",설정!$C$33,$I15)-IF($J15="",설정!$C$34,$J15))),0),CEILING(IF(설정!$C$26="원가 가산",$K15*(1+IF($J15="",설정!$C$34,$J15)),$H15/(1-IF($I15="",설정!$C$33,$I15)-IF($J15="",설정!$C$34,$J15))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M15" s="175" t="n"/>
-      <c r="N15" s="133">
-        <f>IF($L15="","",IF($M15="",$L15,$M15))</f>
-        <v/>
-      </c>
-      <c r="O15" s="133">
-        <f>IF($N15="","",IF(설정!$C$26="원가 가산",$H15*IF($I15="",설정!$C$33,$I15),$N15*IF($I15="",설정!$C$33,$I15)))</f>
-        <v/>
-      </c>
-      <c r="P15" s="133">
-        <f>IF($N15="","",$N15-$H15-$O15)</f>
-        <v/>
-      </c>
-      <c r="Q15" s="176">
-        <f>IF(N($N15)=0,"",$P15/$N15)</f>
-        <v/>
-      </c>
-      <c r="R15" s="176">
-        <f>IF(N($L15)=0,"",$N15/$L15-1)</f>
-        <v/>
-      </c>
-      <c r="S15" s="176">
-        <f>IF(N($K15)=0,"",$N15/$K15-1)</f>
-        <v/>
-      </c>
-      <c r="T15" s="132" t="n"/>
-      <c r="U15" s="133">
-        <f>IF($N15="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N15*(1+IF($T15="",설정!$C$28,$T15)),$N15/(1-IF($T15="",설정!$C$28,$T15))),0),CEILING(IF(설정!$C$26="원가 가산",$N15*(1+IF($T15="",설정!$C$28,$T15)),$N15/(1-IF($T15="",설정!$C$28,$T15))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V15" s="133">
-        <f>IF($N15="","",$N15*$G15)</f>
-        <v/>
-      </c>
-      <c r="W15" s="133">
-        <f>IF($P15="","",$P15*$G15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="171" t="n"/>
-      <c r="C16" s="171" t="n"/>
-      <c r="D16" s="172">
-        <f>IF($C16="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C16,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E16" s="173" t="n"/>
-      <c r="F16" s="133">
-        <f>IF($E16&lt;&gt;"",$E16,IF(N($D16)=0,"",$D16))</f>
-        <v/>
-      </c>
-      <c r="G16" s="174" t="n"/>
-      <c r="H16" s="133">
-        <f>IF($F16="","",$F16*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I16" s="132" t="n"/>
-      <c r="J16" s="132" t="n"/>
-      <c r="K16" s="133">
-        <f>IF($H16="","",IFERROR(IF(설정!$C$26="원가 가산",$H16*(1+IF($I16="",설정!$C$33,$I16)),$H16/(1-IF($I16="",설정!$C$33,$I16))),0))</f>
-        <v/>
-      </c>
-      <c r="L16" s="133">
-        <f>IF($H16="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K16*(1+IF($J16="",설정!$C$34,$J16)),$H16/(1-IF($I16="",설정!$C$33,$I16)-IF($J16="",설정!$C$34,$J16))),0),CEILING(IF(설정!$C$26="원가 가산",$K16*(1+IF($J16="",설정!$C$34,$J16)),$H16/(1-IF($I16="",설정!$C$33,$I16)-IF($J16="",설정!$C$34,$J16))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M16" s="175" t="n"/>
-      <c r="N16" s="133">
-        <f>IF($L16="","",IF($M16="",$L16,$M16))</f>
-        <v/>
-      </c>
-      <c r="O16" s="133">
-        <f>IF($N16="","",IF(설정!$C$26="원가 가산",$H16*IF($I16="",설정!$C$33,$I16),$N16*IF($I16="",설정!$C$33,$I16)))</f>
-        <v/>
-      </c>
-      <c r="P16" s="133">
-        <f>IF($N16="","",$N16-$H16-$O16)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="176">
-        <f>IF(N($N16)=0,"",$P16/$N16)</f>
-        <v/>
-      </c>
-      <c r="R16" s="176">
-        <f>IF(N($L16)=0,"",$N16/$L16-1)</f>
-        <v/>
-      </c>
-      <c r="S16" s="176">
-        <f>IF(N($K16)=0,"",$N16/$K16-1)</f>
-        <v/>
-      </c>
-      <c r="T16" s="132" t="n"/>
-      <c r="U16" s="133">
-        <f>IF($N16="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N16*(1+IF($T16="",설정!$C$28,$T16)),$N16/(1-IF($T16="",설정!$C$28,$T16))),0),CEILING(IF(설정!$C$26="원가 가산",$N16*(1+IF($T16="",설정!$C$28,$T16)),$N16/(1-IF($T16="",설정!$C$28,$T16))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V16" s="133">
-        <f>IF($N16="","",$N16*$G16)</f>
-        <v/>
-      </c>
-      <c r="W16" s="133">
-        <f>IF($P16="","",$P16*$G16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="171" t="n"/>
-      <c r="C17" s="171" t="n"/>
-      <c r="D17" s="172">
-        <f>IF($C17="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C17,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E17" s="173" t="n"/>
-      <c r="F17" s="133">
-        <f>IF($E17&lt;&gt;"",$E17,IF(N($D17)=0,"",$D17))</f>
-        <v/>
-      </c>
-      <c r="G17" s="174" t="n"/>
-      <c r="H17" s="133">
-        <f>IF($F17="","",$F17*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I17" s="132" t="n"/>
-      <c r="J17" s="132" t="n"/>
-      <c r="K17" s="133">
-        <f>IF($H17="","",IFERROR(IF(설정!$C$26="원가 가산",$H17*(1+IF($I17="",설정!$C$33,$I17)),$H17/(1-IF($I17="",설정!$C$33,$I17))),0))</f>
-        <v/>
-      </c>
-      <c r="L17" s="133">
-        <f>IF($H17="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K17*(1+IF($J17="",설정!$C$34,$J17)),$H17/(1-IF($I17="",설정!$C$33,$I17)-IF($J17="",설정!$C$34,$J17))),0),CEILING(IF(설정!$C$26="원가 가산",$K17*(1+IF($J17="",설정!$C$34,$J17)),$H17/(1-IF($I17="",설정!$C$33,$I17)-IF($J17="",설정!$C$34,$J17))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M17" s="175" t="n"/>
-      <c r="N17" s="133">
-        <f>IF($L17="","",IF($M17="",$L17,$M17))</f>
-        <v/>
-      </c>
-      <c r="O17" s="133">
-        <f>IF($N17="","",IF(설정!$C$26="원가 가산",$H17*IF($I17="",설정!$C$33,$I17),$N17*IF($I17="",설정!$C$33,$I17)))</f>
-        <v/>
-      </c>
-      <c r="P17" s="133">
-        <f>IF($N17="","",$N17-$H17-$O17)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="176">
-        <f>IF(N($N17)=0,"",$P17/$N17)</f>
-        <v/>
-      </c>
-      <c r="R17" s="176">
-        <f>IF(N($L17)=0,"",$N17/$L17-1)</f>
-        <v/>
-      </c>
-      <c r="S17" s="176">
-        <f>IF(N($K17)=0,"",$N17/$K17-1)</f>
-        <v/>
-      </c>
-      <c r="T17" s="132" t="n"/>
-      <c r="U17" s="133">
-        <f>IF($N17="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N17*(1+IF($T17="",설정!$C$28,$T17)),$N17/(1-IF($T17="",설정!$C$28,$T17))),0),CEILING(IF(설정!$C$26="원가 가산",$N17*(1+IF($T17="",설정!$C$28,$T17)),$N17/(1-IF($T17="",설정!$C$28,$T17))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V17" s="133">
-        <f>IF($N17="","",$N17*$G17)</f>
-        <v/>
-      </c>
-      <c r="W17" s="133">
-        <f>IF($P17="","",$P17*$G17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="171" t="n"/>
-      <c r="C18" s="171" t="n"/>
-      <c r="D18" s="172">
-        <f>IF($C18="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C18,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E18" s="173" t="n"/>
-      <c r="F18" s="133">
-        <f>IF($E18&lt;&gt;"",$E18,IF(N($D18)=0,"",$D18))</f>
-        <v/>
-      </c>
-      <c r="G18" s="174" t="n"/>
-      <c r="H18" s="133">
-        <f>IF($F18="","",$F18*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I18" s="132" t="n"/>
-      <c r="J18" s="132" t="n"/>
-      <c r="K18" s="133">
-        <f>IF($H18="","",IFERROR(IF(설정!$C$26="원가 가산",$H18*(1+IF($I18="",설정!$C$33,$I18)),$H18/(1-IF($I18="",설정!$C$33,$I18))),0))</f>
-        <v/>
-      </c>
-      <c r="L18" s="133">
-        <f>IF($H18="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K18*(1+IF($J18="",설정!$C$34,$J18)),$H18/(1-IF($I18="",설정!$C$33,$I18)-IF($J18="",설정!$C$34,$J18))),0),CEILING(IF(설정!$C$26="원가 가산",$K18*(1+IF($J18="",설정!$C$34,$J18)),$H18/(1-IF($I18="",설정!$C$33,$I18)-IF($J18="",설정!$C$34,$J18))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M18" s="175" t="n"/>
-      <c r="N18" s="133">
-        <f>IF($L18="","",IF($M18="",$L18,$M18))</f>
-        <v/>
-      </c>
-      <c r="O18" s="133">
-        <f>IF($N18="","",IF(설정!$C$26="원가 가산",$H18*IF($I18="",설정!$C$33,$I18),$N18*IF($I18="",설정!$C$33,$I18)))</f>
-        <v/>
-      </c>
-      <c r="P18" s="133">
-        <f>IF($N18="","",$N18-$H18-$O18)</f>
-        <v/>
-      </c>
-      <c r="Q18" s="176">
-        <f>IF(N($N18)=0,"",$P18/$N18)</f>
-        <v/>
-      </c>
-      <c r="R18" s="176">
-        <f>IF(N($L18)=0,"",$N18/$L18-1)</f>
-        <v/>
-      </c>
-      <c r="S18" s="176">
-        <f>IF(N($K18)=0,"",$N18/$K18-1)</f>
-        <v/>
-      </c>
-      <c r="T18" s="132" t="n"/>
-      <c r="U18" s="133">
-        <f>IF($N18="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N18*(1+IF($T18="",설정!$C$28,$T18)),$N18/(1-IF($T18="",설정!$C$28,$T18))),0),CEILING(IF(설정!$C$26="원가 가산",$N18*(1+IF($T18="",설정!$C$28,$T18)),$N18/(1-IF($T18="",설정!$C$28,$T18))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V18" s="133">
-        <f>IF($N18="","",$N18*$G18)</f>
-        <v/>
-      </c>
-      <c r="W18" s="133">
-        <f>IF($P18="","",$P18*$G18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="171" t="n"/>
-      <c r="C19" s="171" t="n"/>
-      <c r="D19" s="172">
-        <f>IF($C19="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C19,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E19" s="173" t="n"/>
-      <c r="F19" s="133">
-        <f>IF($E19&lt;&gt;"",$E19,IF(N($D19)=0,"",$D19))</f>
-        <v/>
-      </c>
-      <c r="G19" s="174" t="n"/>
-      <c r="H19" s="133">
-        <f>IF($F19="","",$F19*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I19" s="132" t="n"/>
-      <c r="J19" s="132" t="n"/>
-      <c r="K19" s="133">
-        <f>IF($H19="","",IFERROR(IF(설정!$C$26="원가 가산",$H19*(1+IF($I19="",설정!$C$33,$I19)),$H19/(1-IF($I19="",설정!$C$33,$I19))),0))</f>
-        <v/>
-      </c>
-      <c r="L19" s="133">
-        <f>IF($H19="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K19*(1+IF($J19="",설정!$C$34,$J19)),$H19/(1-IF($I19="",설정!$C$33,$I19)-IF($J19="",설정!$C$34,$J19))),0),CEILING(IF(설정!$C$26="원가 가산",$K19*(1+IF($J19="",설정!$C$34,$J19)),$H19/(1-IF($I19="",설정!$C$33,$I19)-IF($J19="",설정!$C$34,$J19))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M19" s="175" t="n"/>
-      <c r="N19" s="133">
-        <f>IF($L19="","",IF($M19="",$L19,$M19))</f>
-        <v/>
-      </c>
-      <c r="O19" s="133">
-        <f>IF($N19="","",IF(설정!$C$26="원가 가산",$H19*IF($I19="",설정!$C$33,$I19),$N19*IF($I19="",설정!$C$33,$I19)))</f>
-        <v/>
-      </c>
-      <c r="P19" s="133">
-        <f>IF($N19="","",$N19-$H19-$O19)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="176">
-        <f>IF(N($N19)=0,"",$P19/$N19)</f>
-        <v/>
-      </c>
-      <c r="R19" s="176">
-        <f>IF(N($L19)=0,"",$N19/$L19-1)</f>
-        <v/>
-      </c>
-      <c r="S19" s="176">
-        <f>IF(N($K19)=0,"",$N19/$K19-1)</f>
-        <v/>
-      </c>
-      <c r="T19" s="132" t="n"/>
-      <c r="U19" s="133">
-        <f>IF($N19="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N19*(1+IF($T19="",설정!$C$28,$T19)),$N19/(1-IF($T19="",설정!$C$28,$T19))),0),CEILING(IF(설정!$C$26="원가 가산",$N19*(1+IF($T19="",설정!$C$28,$T19)),$N19/(1-IF($T19="",설정!$C$28,$T19))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V19" s="133">
-        <f>IF($N19="","",$N19*$G19)</f>
-        <v/>
-      </c>
-      <c r="W19" s="133">
-        <f>IF($P19="","",$P19*$G19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="171" t="n"/>
-      <c r="C20" s="171" t="n"/>
-      <c r="D20" s="172">
-        <f>IF($C20="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C20,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E20" s="173" t="n"/>
-      <c r="F20" s="133">
-        <f>IF($E20&lt;&gt;"",$E20,IF(N($D20)=0,"",$D20))</f>
-        <v/>
-      </c>
-      <c r="G20" s="174" t="n"/>
-      <c r="H20" s="133">
-        <f>IF($F20="","",$F20*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I20" s="132" t="n"/>
-      <c r="J20" s="132" t="n"/>
-      <c r="K20" s="133">
-        <f>IF($H20="","",IFERROR(IF(설정!$C$26="원가 가산",$H20*(1+IF($I20="",설정!$C$33,$I20)),$H20/(1-IF($I20="",설정!$C$33,$I20))),0))</f>
-        <v/>
-      </c>
-      <c r="L20" s="133">
-        <f>IF($H20="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K20*(1+IF($J20="",설정!$C$34,$J20)),$H20/(1-IF($I20="",설정!$C$33,$I20)-IF($J20="",설정!$C$34,$J20))),0),CEILING(IF(설정!$C$26="원가 가산",$K20*(1+IF($J20="",설정!$C$34,$J20)),$H20/(1-IF($I20="",설정!$C$33,$I20)-IF($J20="",설정!$C$34,$J20))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M20" s="175" t="n"/>
-      <c r="N20" s="133">
-        <f>IF($L20="","",IF($M20="",$L20,$M20))</f>
-        <v/>
-      </c>
-      <c r="O20" s="133">
-        <f>IF($N20="","",IF(설정!$C$26="원가 가산",$H20*IF($I20="",설정!$C$33,$I20),$N20*IF($I20="",설정!$C$33,$I20)))</f>
-        <v/>
-      </c>
-      <c r="P20" s="133">
-        <f>IF($N20="","",$N20-$H20-$O20)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="176">
-        <f>IF(N($N20)=0,"",$P20/$N20)</f>
-        <v/>
-      </c>
-      <c r="R20" s="176">
-        <f>IF(N($L20)=0,"",$N20/$L20-1)</f>
-        <v/>
-      </c>
-      <c r="S20" s="176">
-        <f>IF(N($K20)=0,"",$N20/$K20-1)</f>
-        <v/>
-      </c>
-      <c r="T20" s="132" t="n"/>
-      <c r="U20" s="133">
-        <f>IF($N20="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N20*(1+IF($T20="",설정!$C$28,$T20)),$N20/(1-IF($T20="",설정!$C$28,$T20))),0),CEILING(IF(설정!$C$26="원가 가산",$N20*(1+IF($T20="",설정!$C$28,$T20)),$N20/(1-IF($T20="",설정!$C$28,$T20))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V20" s="133">
-        <f>IF($N20="","",$N20*$G20)</f>
-        <v/>
-      </c>
-      <c r="W20" s="133">
-        <f>IF($P20="","",$P20*$G20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="171" t="n"/>
-      <c r="C21" s="171" t="n"/>
-      <c r="D21" s="172">
-        <f>IF($C21="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C21,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E21" s="173" t="n"/>
-      <c r="F21" s="133">
-        <f>IF($E21&lt;&gt;"",$E21,IF(N($D21)=0,"",$D21))</f>
-        <v/>
-      </c>
-      <c r="G21" s="174" t="n"/>
-      <c r="H21" s="133">
-        <f>IF($F21="","",$F21*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I21" s="132" t="n"/>
-      <c r="J21" s="132" t="n"/>
-      <c r="K21" s="133">
-        <f>IF($H21="","",IFERROR(IF(설정!$C$26="원가 가산",$H21*(1+IF($I21="",설정!$C$33,$I21)),$H21/(1-IF($I21="",설정!$C$33,$I21))),0))</f>
-        <v/>
-      </c>
-      <c r="L21" s="133">
-        <f>IF($H21="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K21*(1+IF($J21="",설정!$C$34,$J21)),$H21/(1-IF($I21="",설정!$C$33,$I21)-IF($J21="",설정!$C$34,$J21))),0),CEILING(IF(설정!$C$26="원가 가산",$K21*(1+IF($J21="",설정!$C$34,$J21)),$H21/(1-IF($I21="",설정!$C$33,$I21)-IF($J21="",설정!$C$34,$J21))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M21" s="175" t="n"/>
-      <c r="N21" s="133">
-        <f>IF($L21="","",IF($M21="",$L21,$M21))</f>
-        <v/>
-      </c>
-      <c r="O21" s="133">
-        <f>IF($N21="","",IF(설정!$C$26="원가 가산",$H21*IF($I21="",설정!$C$33,$I21),$N21*IF($I21="",설정!$C$33,$I21)))</f>
-        <v/>
-      </c>
-      <c r="P21" s="133">
-        <f>IF($N21="","",$N21-$H21-$O21)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="176">
-        <f>IF(N($N21)=0,"",$P21/$N21)</f>
-        <v/>
-      </c>
-      <c r="R21" s="176">
-        <f>IF(N($L21)=0,"",$N21/$L21-1)</f>
-        <v/>
-      </c>
-      <c r="S21" s="176">
-        <f>IF(N($K21)=0,"",$N21/$K21-1)</f>
-        <v/>
-      </c>
-      <c r="T21" s="132" t="n"/>
-      <c r="U21" s="133">
-        <f>IF($N21="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N21*(1+IF($T21="",설정!$C$28,$T21)),$N21/(1-IF($T21="",설정!$C$28,$T21))),0),CEILING(IF(설정!$C$26="원가 가산",$N21*(1+IF($T21="",설정!$C$28,$T21)),$N21/(1-IF($T21="",설정!$C$28,$T21))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V21" s="133">
-        <f>IF($N21="","",$N21*$G21)</f>
-        <v/>
-      </c>
-      <c r="W21" s="133">
-        <f>IF($P21="","",$P21*$G21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="171" t="n"/>
-      <c r="C22" s="171" t="n"/>
-      <c r="D22" s="172">
-        <f>IF($C22="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C22,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E22" s="173" t="n"/>
-      <c r="F22" s="133">
-        <f>IF($E22&lt;&gt;"",$E22,IF(N($D22)=0,"",$D22))</f>
-        <v/>
-      </c>
-      <c r="G22" s="174" t="n"/>
-      <c r="H22" s="133">
-        <f>IF($F22="","",$F22*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I22" s="132" t="n"/>
-      <c r="J22" s="132" t="n"/>
-      <c r="K22" s="133">
-        <f>IF($H22="","",IFERROR(IF(설정!$C$26="원가 가산",$H22*(1+IF($I22="",설정!$C$33,$I22)),$H22/(1-IF($I22="",설정!$C$33,$I22))),0))</f>
-        <v/>
-      </c>
-      <c r="L22" s="133">
-        <f>IF($H22="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K22*(1+IF($J22="",설정!$C$34,$J22)),$H22/(1-IF($I22="",설정!$C$33,$I22)-IF($J22="",설정!$C$34,$J22))),0),CEILING(IF(설정!$C$26="원가 가산",$K22*(1+IF($J22="",설정!$C$34,$J22)),$H22/(1-IF($I22="",설정!$C$33,$I22)-IF($J22="",설정!$C$34,$J22))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M22" s="175" t="n"/>
-      <c r="N22" s="133">
-        <f>IF($L22="","",IF($M22="",$L22,$M22))</f>
-        <v/>
-      </c>
-      <c r="O22" s="133">
-        <f>IF($N22="","",IF(설정!$C$26="원가 가산",$H22*IF($I22="",설정!$C$33,$I22),$N22*IF($I22="",설정!$C$33,$I22)))</f>
-        <v/>
-      </c>
-      <c r="P22" s="133">
-        <f>IF($N22="","",$N22-$H22-$O22)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="176">
-        <f>IF(N($N22)=0,"",$P22/$N22)</f>
-        <v/>
-      </c>
-      <c r="R22" s="176">
-        <f>IF(N($L22)=0,"",$N22/$L22-1)</f>
-        <v/>
-      </c>
-      <c r="S22" s="176">
-        <f>IF(N($K22)=0,"",$N22/$K22-1)</f>
-        <v/>
-      </c>
-      <c r="T22" s="132" t="n"/>
-      <c r="U22" s="133">
-        <f>IF($N22="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N22*(1+IF($T22="",설정!$C$28,$T22)),$N22/(1-IF($T22="",설정!$C$28,$T22))),0),CEILING(IF(설정!$C$26="원가 가산",$N22*(1+IF($T22="",설정!$C$28,$T22)),$N22/(1-IF($T22="",설정!$C$28,$T22))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V22" s="133">
-        <f>IF($N22="","",$N22*$G22)</f>
-        <v/>
-      </c>
-      <c r="W22" s="133">
-        <f>IF($P22="","",$P22*$G22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="171" t="n"/>
-      <c r="C23" s="171" t="n"/>
-      <c r="D23" s="172">
-        <f>IF($C23="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C23,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E23" s="173" t="n"/>
-      <c r="F23" s="133">
-        <f>IF($E23&lt;&gt;"",$E23,IF(N($D23)=0,"",$D23))</f>
-        <v/>
-      </c>
-      <c r="G23" s="174" t="n"/>
-      <c r="H23" s="133">
-        <f>IF($F23="","",$F23*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I23" s="132" t="n"/>
-      <c r="J23" s="132" t="n"/>
-      <c r="K23" s="133">
-        <f>IF($H23="","",IFERROR(IF(설정!$C$26="원가 가산",$H23*(1+IF($I23="",설정!$C$33,$I23)),$H23/(1-IF($I23="",설정!$C$33,$I23))),0))</f>
-        <v/>
-      </c>
-      <c r="L23" s="133">
-        <f>IF($H23="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K23*(1+IF($J23="",설정!$C$34,$J23)),$H23/(1-IF($I23="",설정!$C$33,$I23)-IF($J23="",설정!$C$34,$J23))),0),CEILING(IF(설정!$C$26="원가 가산",$K23*(1+IF($J23="",설정!$C$34,$J23)),$H23/(1-IF($I23="",설정!$C$33,$I23)-IF($J23="",설정!$C$34,$J23))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M23" s="175" t="n"/>
-      <c r="N23" s="133">
-        <f>IF($L23="","",IF($M23="",$L23,$M23))</f>
-        <v/>
-      </c>
-      <c r="O23" s="133">
-        <f>IF($N23="","",IF(설정!$C$26="원가 가산",$H23*IF($I23="",설정!$C$33,$I23),$N23*IF($I23="",설정!$C$33,$I23)))</f>
-        <v/>
-      </c>
-      <c r="P23" s="133">
-        <f>IF($N23="","",$N23-$H23-$O23)</f>
-        <v/>
-      </c>
-      <c r="Q23" s="176">
-        <f>IF(N($N23)=0,"",$P23/$N23)</f>
-        <v/>
-      </c>
-      <c r="R23" s="176">
-        <f>IF(N($L23)=0,"",$N23/$L23-1)</f>
-        <v/>
-      </c>
-      <c r="S23" s="176">
-        <f>IF(N($K23)=0,"",$N23/$K23-1)</f>
-        <v/>
-      </c>
-      <c r="T23" s="132" t="n"/>
-      <c r="U23" s="133">
-        <f>IF($N23="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N23*(1+IF($T23="",설정!$C$28,$T23)),$N23/(1-IF($T23="",설정!$C$28,$T23))),0),CEILING(IF(설정!$C$26="원가 가산",$N23*(1+IF($T23="",설정!$C$28,$T23)),$N23/(1-IF($T23="",설정!$C$28,$T23))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V23" s="133">
-        <f>IF($N23="","",$N23*$G23)</f>
-        <v/>
-      </c>
-      <c r="W23" s="133">
-        <f>IF($P23="","",$P23*$G23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="171" t="n"/>
-      <c r="C24" s="171" t="n"/>
-      <c r="D24" s="172">
-        <f>IF($C24="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C24,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E24" s="173" t="n"/>
-      <c r="F24" s="133">
-        <f>IF($E24&lt;&gt;"",$E24,IF(N($D24)=0,"",$D24))</f>
-        <v/>
-      </c>
-      <c r="G24" s="174" t="n"/>
-      <c r="H24" s="133">
-        <f>IF($F24="","",$F24*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I24" s="132" t="n"/>
-      <c r="J24" s="132" t="n"/>
-      <c r="K24" s="133">
-        <f>IF($H24="","",IFERROR(IF(설정!$C$26="원가 가산",$H24*(1+IF($I24="",설정!$C$33,$I24)),$H24/(1-IF($I24="",설정!$C$33,$I24))),0))</f>
-        <v/>
-      </c>
-      <c r="L24" s="133">
-        <f>IF($H24="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K24*(1+IF($J24="",설정!$C$34,$J24)),$H24/(1-IF($I24="",설정!$C$33,$I24)-IF($J24="",설정!$C$34,$J24))),0),CEILING(IF(설정!$C$26="원가 가산",$K24*(1+IF($J24="",설정!$C$34,$J24)),$H24/(1-IF($I24="",설정!$C$33,$I24)-IF($J24="",설정!$C$34,$J24))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M24" s="175" t="n"/>
-      <c r="N24" s="133">
-        <f>IF($L24="","",IF($M24="",$L24,$M24))</f>
-        <v/>
-      </c>
-      <c r="O24" s="133">
-        <f>IF($N24="","",IF(설정!$C$26="원가 가산",$H24*IF($I24="",설정!$C$33,$I24),$N24*IF($I24="",설정!$C$33,$I24)))</f>
-        <v/>
-      </c>
-      <c r="P24" s="133">
-        <f>IF($N24="","",$N24-$H24-$O24)</f>
-        <v/>
-      </c>
-      <c r="Q24" s="176">
-        <f>IF(N($N24)=0,"",$P24/$N24)</f>
-        <v/>
-      </c>
-      <c r="R24" s="176">
-        <f>IF(N($L24)=0,"",$N24/$L24-1)</f>
-        <v/>
-      </c>
-      <c r="S24" s="176">
-        <f>IF(N($K24)=0,"",$N24/$K24-1)</f>
-        <v/>
-      </c>
-      <c r="T24" s="132" t="n"/>
-      <c r="U24" s="133">
-        <f>IF($N24="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N24*(1+IF($T24="",설정!$C$28,$T24)),$N24/(1-IF($T24="",설정!$C$28,$T24))),0),CEILING(IF(설정!$C$26="원가 가산",$N24*(1+IF($T24="",설정!$C$28,$T24)),$N24/(1-IF($T24="",설정!$C$28,$T24))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V24" s="133">
-        <f>IF($N24="","",$N24*$G24)</f>
-        <v/>
-      </c>
-      <c r="W24" s="133">
-        <f>IF($P24="","",$P24*$G24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="171" t="n"/>
-      <c r="C25" s="171" t="n"/>
-      <c r="D25" s="172">
-        <f>IF($C25="","",IFERROR(INDEX(자재판매가산출!$K$6:$K$24,MATCH($C25,자재판매가산출!$C$6:$C$24,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E25" s="173" t="n"/>
-      <c r="F25" s="133">
-        <f>IF($E25&lt;&gt;"",$E25,IF(N($D25)=0,"",$D25))</f>
-        <v/>
-      </c>
-      <c r="G25" s="174" t="n"/>
-      <c r="H25" s="133">
-        <f>IF($F25="","",$F25*(1+설정!$C$32))</f>
-        <v/>
-      </c>
-      <c r="I25" s="132" t="n"/>
-      <c r="J25" s="132" t="n"/>
-      <c r="K25" s="133">
-        <f>IF($H25="","",IFERROR(IF(설정!$C$26="원가 가산",$H25*(1+IF($I25="",설정!$C$33,$I25)),$H25/(1-IF($I25="",설정!$C$33,$I25))),0))</f>
-        <v/>
-      </c>
-      <c r="L25" s="133">
-        <f>IF($H25="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$K25*(1+IF($J25="",설정!$C$34,$J25)),$H25/(1-IF($I25="",설정!$C$33,$I25)-IF($J25="",설정!$C$34,$J25))),0),CEILING(IF(설정!$C$26="원가 가산",$K25*(1+IF($J25="",설정!$C$34,$J25)),$H25/(1-IF($I25="",설정!$C$33,$I25)-IF($J25="",설정!$C$34,$J25))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="M25" s="175" t="n"/>
-      <c r="N25" s="133">
-        <f>IF($L25="","",IF($M25="",$L25,$M25))</f>
-        <v/>
-      </c>
-      <c r="O25" s="133">
-        <f>IF($N25="","",IF(설정!$C$26="원가 가산",$H25*IF($I25="",설정!$C$33,$I25),$N25*IF($I25="",설정!$C$33,$I25)))</f>
-        <v/>
-      </c>
-      <c r="P25" s="133">
-        <f>IF($N25="","",$N25-$H25-$O25)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="176">
-        <f>IF(N($N25)=0,"",$P25/$N25)</f>
-        <v/>
-      </c>
-      <c r="R25" s="176">
-        <f>IF(N($L25)=0,"",$N25/$L25-1)</f>
-        <v/>
-      </c>
-      <c r="S25" s="176">
-        <f>IF(N($K25)=0,"",$N25/$K25-1)</f>
-        <v/>
-      </c>
-      <c r="T25" s="132" t="n"/>
-      <c r="U25" s="133">
-        <f>IF($N25="","",IFERROR(IF(설정!$C$27&lt;=1,ROUND(IF(설정!$C$26="원가 가산",$N25*(1+IF($T25="",설정!$C$28,$T25)),$N25/(1-IF($T25="",설정!$C$28,$T25))),0),CEILING(IF(설정!$C$26="원가 가산",$N25*(1+IF($T25="",설정!$C$28,$T25)),$N25/(1-IF($T25="",설정!$C$28,$T25))),설정!$C$27)),0))</f>
-        <v/>
-      </c>
-      <c r="V25" s="133">
-        <f>IF($N25="","",$N25*$G25)</f>
-        <v/>
-      </c>
-      <c r="W25" s="133">
-        <f>IF($P25="","",$P25*$G25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="147" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="C26" s="137" t="n"/>
-      <c r="D26" s="137" t="n"/>
-      <c r="E26" s="137" t="n"/>
-      <c r="F26" s="137" t="n"/>
-      <c r="G26" s="177">
-        <f>SUM(G6:G25)</f>
-        <v/>
-      </c>
-      <c r="H26" s="137" t="n"/>
-      <c r="I26" s="137" t="n"/>
-      <c r="J26" s="137" t="n"/>
-      <c r="K26" s="137" t="n"/>
-      <c r="L26" s="137" t="n"/>
-      <c r="M26" s="137" t="n"/>
-      <c r="N26" s="137" t="n"/>
-      <c r="O26" s="137" t="n"/>
-      <c r="P26" s="137" t="n"/>
-      <c r="Q26" s="178">
-        <f>IFERROR(SUM(W6:W25)/SUM(V6:V25),0)</f>
-        <v/>
-      </c>
-      <c r="R26" s="137" t="n"/>
-      <c r="S26" s="137" t="n"/>
-      <c r="T26" s="137" t="n"/>
-      <c r="U26" s="137" t="n"/>
-      <c r="V26" s="179">
-        <f>SUM(V6:V25)</f>
-        <v/>
-      </c>
-      <c r="W26" s="179">
-        <f>SUM(W6:W25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="138" t="inlineStr">
-        <is>
-          <t>① 품목코드(C열)를 넣으면 자재판매가산출 시트에서 그 품목의 판매단가를 찾아 D열에 가져옵니다 — 그것이 태성 입고가입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="138" t="inlineStr">
-        <is>
-          <t>② D열이 비면 그 코드가 자재판매가산출에 없다는 뜻입니다. 그럴 때는 E열에 입고가를 직접 넣으세요. E열에 값이 있으면 조회값보다 우선합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="138" t="inlineStr">
-        <is>
-          <t>③ 태성 입고가가 곧 원가입니다. 입고 후 운반비 등이 붙으면 설정 C32(태성 추가비용률)에 넣으세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="138" t="inlineStr">
-        <is>
-          <t>④ 판관비율·영업이익률은 설정 C33·C34(태성 기준)를 씁니다. 플로우텍 상품 판매가의 값(C24·C25)과는 별개입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="138" t="inlineStr">
-        <is>
-          <t>⑤ L열 기준 판매가를 영업에 전달하고, 영업이 정한 값을 M열(노란 칸)에 적습니다. 비워 두면 기준가가 그대로 적용됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="139" t="inlineStr">
-        <is>
-          <t>⑥ 최종 판매가가 BEP 가격보다 낮으면 M열이 빨갛게 표시됩니다 — 팔수록 손해라는 뜻입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="138" t="inlineStr">
-        <is>
-          <t>표시 금액은 모두 부가세 별도입니다.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="M6:M25">
-    <cfRule type="expression" priority="1" dxfId="3" stopIfTrue="0">
-      <formula>AND(N($M6)&gt;0,N($K6)&gt;0,$M6&lt;$K6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R6:R25">
-    <cfRule type="expression" priority="2" dxfId="4" stopIfTrue="0">
-      <formula>AND(N($N6)&gt;0,$N6&lt;$L6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="B4:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
@@ -6382,7 +4756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7540,7 +5914,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7950,13 +6324,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D41"/>
+  <dimension ref="B2:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="3.69921875" customWidth="1" min="1" max="1"/>
@@ -8324,112 +6698,57 @@
     <row r="31">
       <c r="B31" s="165" t="inlineStr">
         <is>
-          <t>■ 태성 재판매 (플로우텍 공급 → 태성 입고 → 재판매)</t>
+          <t>■ 범례</t>
         </is>
       </c>
       <c r="C31" s="138" t="n"/>
       <c r="D31" s="15" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="156" t="inlineStr">
-        <is>
-          <t>태성 추가비용률</t>
-        </is>
-      </c>
-      <c r="C32" s="157" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="158" t="inlineStr">
-        <is>
-          <t>태성 입고 후 붙는 운반비 · 보관비 등. 없으면 0%.</t>
-        </is>
-      </c>
+      <c r="B32" s="166" t="inlineStr">
+        <is>
+          <t>노란 채우기</t>
+        </is>
+      </c>
+      <c r="C32" s="138" t="inlineStr">
+        <is>
+          <t>반드시 확인하고 채워야 하는 칸</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" thickBot="1">
-      <c r="B33" s="180" t="inlineStr">
-        <is>
-          <t>태성 판관비율</t>
-        </is>
-      </c>
-      <c r="C33" s="157" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="D33" s="181" t="inlineStr">
-        <is>
-          <t>태성 기준 판매관리비. 플로우텍 판관비(C24)와 별개로 관리합니다.</t>
-        </is>
-      </c>
+      <c r="B33" s="167" t="inlineStr">
+        <is>
+          <t>파란 글씨</t>
+        </is>
+      </c>
+      <c r="C33" s="168" t="inlineStr">
+        <is>
+          <t>직접 입력하는 칸</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="169" t="inlineStr">
         <is>
-          <t>태성 영업이익률</t>
-        </is>
-      </c>
-      <c r="C34" s="157" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D34" s="138" t="inlineStr">
-        <is>
-          <t>태성 기준 판매가에 얹을 목표 영업이익.</t>
+          <t>검정 글씨</t>
+        </is>
+      </c>
+      <c r="C34" s="138" t="inlineStr">
+        <is>
+          <t>수식 — 손대지 마세요</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="162" t="n"/>
-      <c r="C35" s="138" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="182" t="inlineStr">
-        <is>
-          <t>■ 범례</t>
-        </is>
-      </c>
-      <c r="C37" s="138" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="183" t="inlineStr">
-        <is>
-          <t>노란 채우기</t>
-        </is>
-      </c>
-      <c r="C38" s="138" t="inlineStr">
-        <is>
-          <t>반드시 확인하고 채워야 하는 칸</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="184" t="inlineStr">
-        <is>
-          <t>파란 글씨</t>
-        </is>
-      </c>
-      <c r="C39" s="138" t="inlineStr">
-        <is>
-          <t>직접 입력하는 칸</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="169" t="inlineStr">
-        <is>
-          <t>검정 글씨</t>
-        </is>
-      </c>
-      <c r="C40" s="138" t="inlineStr">
-        <is>
-          <t>수식 — 손대지 마세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="162" t="inlineStr">
+      <c r="B35" s="162" t="inlineStr">
         <is>
           <t>초록 글씨</t>
         </is>
       </c>
-      <c r="C41" s="138" t="inlineStr">
+      <c r="C35" s="138" t="inlineStr">
         <is>
           <t>다른 시트를 참조하는 수식</t>
         </is>
@@ -8452,7 +6771,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
